--- a/data/supplementary_tables/Supplementary Table 14.xlsx
+++ b/data/supplementary_tables/Supplementary Table 14.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_rechecked_precise_red/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_verified_red/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AB7ACD-F2AD-A74D-BF62-BCC89310CF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B6FCDE-1C40-F944-BB46-8F0A4D01C100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="629">
   <si>
     <t>Protein_Short_Name</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Rho guanine nucleotide exchange factor</t>
   </si>
   <si>
-    <t>Glycosyltransferase sugar-binding region...</t>
-  </si>
-  <si>
     <t>Involved in regulation of DNA replication</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>Ribosomal Protein S15</t>
   </si>
   <si>
-    <t>Peptidyl-trna Hydrolase Domain Containing...</t>
-  </si>
-  <si>
     <t>Beta-1,4-galactosyltransferase 4</t>
   </si>
   <si>
@@ -136,9 +130,6 @@
     <t>RNA recognition motif</t>
   </si>
   <si>
-    <t>TIGRFAM Haloacid Dehalogenase...</t>
-  </si>
-  <si>
     <t>Eif-2</t>
   </si>
   <si>
@@ -166,9 +157,6 @@
     <t>Trna Cytidylyltransferase Activity</t>
   </si>
   <si>
-    <t>Haloacid dehalogenase domain protein...</t>
-  </si>
-  <si>
     <t>ATP-dependent DNA helicase implicated in</t>
   </si>
   <si>
@@ -208,12 +196,6 @@
     <t>Acts as a Ras effector</t>
   </si>
   <si>
-    <t>Binds double-stranded DNA tightly but</t>
-  </si>
-  <si>
-    <t>Integrin, alpha 3 (antigen CD49C,</t>
-  </si>
-  <si>
     <t>Gamma-glutamylcyclotransferase isoform X1</t>
   </si>
   <si>
@@ -232,12 +214,6 @@
     <t>Substrate-specific Adapter of An E3</t>
   </si>
   <si>
-    <t>Eca and bai are essential,</t>
-  </si>
-  <si>
-    <t>Displays antiviral activity against...</t>
-  </si>
-  <si>
     <t>Methyltransferase</t>
   </si>
   <si>
@@ -295,9 +271,6 @@
     <t>Catalyzes the last two sequential</t>
   </si>
   <si>
-    <t>Dual specificity protein phosphatase,...</t>
-  </si>
-  <si>
     <t>Endoplasmic reticulum resident protein</t>
   </si>
   <si>
@@ -310,18 +283,12 @@
     <t>Eukaryotic Ribosomal Protein El34 Family</t>
   </si>
   <si>
-    <t>Binds 16S rRNA</t>
-  </si>
-  <si>
     <t>Ribosomal L22e protein family</t>
   </si>
   <si>
     <t>DNA-dependent RNA polymerase</t>
   </si>
   <si>
-    <t>Vacuolar protein sorting-associated...</t>
-  </si>
-  <si>
     <t>Assembly Chaperone 3</t>
   </si>
   <si>
@@ -352,18 +319,9 @@
     <t>Promotes the exchange of GDP</t>
   </si>
   <si>
-    <t>Uptake of acetate and succinate.</t>
-  </si>
-  <si>
-    <t>HAMP (Histidine kinases, Adenylyl...</t>
-  </si>
-  <si>
     <t>Proteasome assembly chaperone 3</t>
   </si>
   <si>
-    <t>Introduces a single-strand break via</t>
-  </si>
-  <si>
     <t>Late Endosomal Lysosomal Adaptor, MAPK</t>
   </si>
   <si>
@@ -379,9 +337,6 @@
     <t>Translocon-associated protein</t>
   </si>
   <si>
-    <t>Is probably</t>
-  </si>
-  <si>
     <t>EAP30/Vps36 family</t>
   </si>
   <si>
@@ -436,15 +391,9 @@
     <t>2-epimerase</t>
   </si>
   <si>
-    <t>Large family of predicted...</t>
-  </si>
-  <si>
     <t>Carbonic anhydrase</t>
   </si>
   <si>
-    <t>Uncharacterized conserved protein...</t>
-  </si>
-  <si>
     <t>Dynein light chain roadblock-type 1</t>
   </si>
   <si>
@@ -472,24 +421,15 @@
     <t>DNA-dependent 3'-5' helicase</t>
   </si>
   <si>
-    <t>In elementary bodies (EBs, the</t>
-  </si>
-  <si>
     <t>Protein Complex 4 Mu 1 Subunit</t>
   </si>
   <si>
-    <t>PFAM nucleic acid binding, OB-fold,</t>
-  </si>
-  <si>
     <t>Rab GTPase</t>
   </si>
   <si>
     <t>Phospholipid scramblase</t>
   </si>
   <si>
-    <t>Translocon-associated protein (TRAP),...</t>
-  </si>
-  <si>
     <t>Signal Recognition Particle</t>
   </si>
   <si>
@@ -529,15 +469,9 @@
     <t>Exonuclease</t>
   </si>
   <si>
-    <t>Zinc Metalloprotease Whose Natural...</t>
-  </si>
-  <si>
     <t>Vacuolar fusion protein MON1</t>
   </si>
   <si>
-    <t>Chemotaxis signal transduction system...</t>
-  </si>
-  <si>
     <t>DNA-directed RNA polymerases I, II,</t>
   </si>
   <si>
@@ -550,9 +484,6 @@
     <t>Transmembrane Protein 106A</t>
   </si>
   <si>
-    <t>Function Specifically Implies SEC24C and</t>
-  </si>
-  <si>
     <t>Arrestin domain-containing protein 3</t>
   </si>
   <si>
@@ -571,15 +502,9 @@
     <t>Dihydroxyacetone binding subunit of the</t>
   </si>
   <si>
-    <t>Transmembrane emp24 protein transport...</t>
-  </si>
-  <si>
     <t>DNA photolyase family</t>
   </si>
   <si>
-    <t>Positively</t>
-  </si>
-  <si>
     <t>Transmembrane Protein 182</t>
   </si>
   <si>
@@ -610,48 +535,27 @@
     <t>Serine threonine-protein phosphatase 2A 65</t>
   </si>
   <si>
-    <t>Calcium calmodulin-dependent protein...</t>
-  </si>
-  <si>
     <t>Chromosome 15 open reading frame 41</t>
   </si>
   <si>
     <t>Shikimate</t>
   </si>
   <si>
-    <t>Desiccation protectant protein Lea14...</t>
-  </si>
-  <si>
     <t>Galactinol synthase</t>
   </si>
   <si>
     <t>Fuzzy planar cell polarity protein</t>
   </si>
   <si>
-    <t>Predicted SAM-dependent RNA...</t>
-  </si>
-  <si>
     <t>Enzyme 2</t>
   </si>
   <si>
-    <t>Probable Brix domain-containing ribosomal...</t>
-  </si>
-  <si>
-    <t>Catalyzes the GTP-dependent ribosomal...</t>
-  </si>
-  <si>
     <t>Peptidase A4 family</t>
   </si>
   <si>
     <t>SEC14-like protein 2</t>
   </si>
   <si>
-    <t>Ubiquitin-associated Domain-containing...</t>
-  </si>
-  <si>
-    <t>F-actin-capping proteins bind in a</t>
-  </si>
-  <si>
     <t>Positive Regulation of TORC1 Signaling</t>
   </si>
   <si>
@@ -676,18 +580,9 @@
     <t>Coiled-coil</t>
   </si>
   <si>
-    <t>Gene with more than two</t>
-  </si>
-  <si>
-    <t>Plays a major role in</t>
-  </si>
-  <si>
     <t>Uracil-DNA glycosylase</t>
   </si>
   <si>
-    <t>Involved in the secretory pathway</t>
-  </si>
-  <si>
     <t>Sigma Non-opioid Intracellular Receptor</t>
   </si>
   <si>
@@ -700,9 +595,6 @@
     <t>ADP-ribosylation factor-like protein</t>
   </si>
   <si>
-    <t>Mannose-6-phosphate Isomerase Type 2...</t>
-  </si>
-  <si>
     <t>Function in general translation initiation</t>
   </si>
   <si>
@@ -718,15 +610,9 @@
     <t>Ras of Complex, Roc, domain of DAPkinase</t>
   </si>
   <si>
-    <t>Probable meiosis-specific protein SPO11...</t>
-  </si>
-  <si>
     <t>COG2270 Permeases of the major</t>
   </si>
   <si>
-    <t>Cullin-associated NEDD8-dissociated...</t>
-  </si>
-  <si>
     <t>Pesticidal crystal protein Cry9Ea</t>
   </si>
   <si>
@@ -748,12 +634,6 @@
     <t>EGF stimulates the growth of</t>
   </si>
   <si>
-    <t>Galactinol--sucrose...</t>
-  </si>
-  <si>
-    <t>In complex with CCZ1, is</t>
-  </si>
-  <si>
     <t>Vacuolar protein</t>
   </si>
   <si>
@@ -790,9 +670,6 @@
     <t>Hexose phosphate transport protein</t>
   </si>
   <si>
-    <t>Protein Serine/threonine Phosphatase...</t>
-  </si>
-  <si>
     <t>Spondin-1-like protein</t>
   </si>
   <si>
@@ -805,21 +682,9 @@
     <t>Involved in nucleolar processing of</t>
   </si>
   <si>
-    <t>Occurring C-terminal to Leucine-rich...</t>
-  </si>
-  <si>
-    <t>Protein N-acetylglucosaminyltransferase...</t>
-  </si>
-  <si>
     <t>Collagenase</t>
   </si>
   <si>
-    <t>Trafficking protein particle complex...</t>
-  </si>
-  <si>
-    <t>Peptide-n(4)-(n-acetyl-beta-...</t>
-  </si>
-  <si>
     <t>Pantothenate kinase</t>
   </si>
   <si>
@@ -832,15 +697,9 @@
     <t>Retrotransposon-like protein 1</t>
   </si>
   <si>
-    <t>Permuted papain-like amidase enzyme,...</t>
-  </si>
-  <si>
     <t>F-box WD repeat-containing protein 9</t>
   </si>
   <si>
-    <t>SREBP-SCAP complex retention in...</t>
-  </si>
-  <si>
     <t>SLA1 homology domain 1, SHD1</t>
   </si>
   <si>
@@ -892,18 +751,12 @@
     <t>Signal recognition particle receptor beta</t>
   </si>
   <si>
-    <t>This protein</t>
-  </si>
-  <si>
     <t>Gelsolin homology domain</t>
   </si>
   <si>
     <t>This enzyme acetylates the N-terminal</t>
   </si>
   <si>
-    <t>Retinal pigment epithelial membrane...</t>
-  </si>
-  <si>
     <t>Skeletal Muscle Satellite Cell Migration</t>
   </si>
   <si>
@@ -919,9 +772,6 @@
     <t>Snrnp Sm Proteins Family</t>
   </si>
   <si>
-    <t>Integrins alpha-1 beta-1, alpha-2 beta-1,</t>
-  </si>
-  <si>
     <t>Apoptotic Process</t>
   </si>
   <si>
@@ -940,15 +790,9 @@
     <t>Non-catalytic component of the exosome</t>
   </si>
   <si>
-    <t>Structure-specific nuclease with 5'-flap...</t>
-  </si>
-  <si>
     <t>Poly(adp-ribose) Glycohydrolase</t>
   </si>
   <si>
-    <t>Constituent of COPII-coated endoplasmic...</t>
-  </si>
-  <si>
     <t>C2 domain</t>
   </si>
   <si>
@@ -988,42 +832,21 @@
     <t>Formation of pseudouridine at positions</t>
   </si>
   <si>
-    <t>Phosphatidylinositol glycan anchor...</t>
-  </si>
-  <si>
     <t>Leucine Rich repeats (2 copies)</t>
   </si>
   <si>
     <t>Myosin-binding protein H</t>
   </si>
   <si>
-    <t>Probably</t>
-  </si>
-  <si>
-    <t>Required for muscle development probably</t>
-  </si>
-  <si>
-    <t>Directs the termination of nascent</t>
-  </si>
-  <si>
-    <t>Could be</t>
-  </si>
-  <si>
     <t>Phe-4-hydroxylase</t>
   </si>
   <si>
-    <t>Catalyzes the hydrolysis of inorganic</t>
-  </si>
-  <si>
     <t>Small ribosomal subunit protein eS25</t>
   </si>
   <si>
     <t>Transposase</t>
   </si>
   <si>
-    <t>N-acetylglucosaminyl-proteoglycan...</t>
-  </si>
-  <si>
     <t>DNA repair helicase</t>
   </si>
   <si>
@@ -1054,9 +877,6 @@
     <t>Delta-type Opioid Receptor Binding</t>
   </si>
   <si>
-    <t>COG0123 Deacetylases, including yeast...</t>
-  </si>
-  <si>
     <t>SDA1</t>
   </si>
   <si>
@@ -1069,24 +889,15 @@
     <t>Resistance protein</t>
   </si>
   <si>
-    <t>Determination of Stomach Left/right...</t>
-  </si>
-  <si>
     <t>Zgc 66475</t>
   </si>
   <si>
-    <t>S-adenosyl-L-methionine-dependent...</t>
-  </si>
-  <si>
     <t>Uncharacterized protein family UPF0016</t>
   </si>
   <si>
     <t>RAB13, member RAS oncogene family</t>
   </si>
   <si>
-    <t>Displays glyoxalase activity, catalyzing...</t>
-  </si>
-  <si>
     <t>Class-ii Aminoacyl-trna Synthetase Family</t>
   </si>
   <si>
@@ -1144,12 +955,6 @@
     <t>U6 snRNA-associated Sm-like protein</t>
   </si>
   <si>
-    <t>Binds to 23S rRNA.</t>
-  </si>
-  <si>
-    <t>PhpP and its cognate protein</t>
-  </si>
-  <si>
     <t>eIF-2B alpha/beta/delta</t>
   </si>
   <si>
@@ -1159,18 +964,12 @@
     <t>Lys-63-specific deubiquitinase BRCC36</t>
   </si>
   <si>
-    <t>Ubiquinol-cytochrome C Reductase Complex...</t>
-  </si>
-  <si>
     <t>Lipid Droplet Organization</t>
   </si>
   <si>
     <t>Type-b Carboxylesterase Lipase Family</t>
   </si>
   <si>
-    <t>Binds directly to 23S rRNA.</t>
-  </si>
-  <si>
     <t>Leucine-rich repeat-containing protein 7</t>
   </si>
   <si>
@@ -1180,21 +979,12 @@
     <t>ATP-dependent DNA helicase</t>
   </si>
   <si>
-    <t>Involved in the activation and</t>
-  </si>
-  <si>
     <t>Nucleotidyltransferase domain</t>
   </si>
   <si>
-    <t>Asparagine Catabolic Process via...</t>
-  </si>
-  <si>
     <t>AP-5 complex subunit beta-1</t>
   </si>
   <si>
-    <t>Prostaglandin f2-alpha synthase...</t>
-  </si>
-  <si>
     <t>Clathrin adaptor complex small chain</t>
   </si>
   <si>
@@ -1213,30 +1003,15 @@
     <t>NACHT domain</t>
   </si>
   <si>
-    <t>Nuclear Receptor Transcription...</t>
-  </si>
-  <si>
-    <t>Negative Regulation of Constitutive...</t>
-  </si>
-  <si>
     <t>Murine retrovirus integration site 1</t>
   </si>
   <si>
     <t>Topoisomerase</t>
   </si>
   <si>
-    <t>Neutral/alkaline non-lysosomal...</t>
-  </si>
-  <si>
     <t>Glycosyl hydrolase</t>
   </si>
   <si>
-    <t>Binds LPA with Higher Affinity Than Pip2.</t>
-  </si>
-  <si>
-    <t>Initiates blood coagulation by forming</t>
-  </si>
-  <si>
     <t>Aldo Keto Reductase Family</t>
   </si>
   <si>
@@ -1255,9 +1030,6 @@
     <t>DNA polymerase</t>
   </si>
   <si>
-    <t>Serine Threonine-protein Phosphatase 6...</t>
-  </si>
-  <si>
     <t>Retinol dehydrogenase 12</t>
   </si>
   <si>
@@ -1273,27 +1045,12 @@
     <t>ATP binding to DnaK triggers</t>
   </si>
   <si>
-    <t>Class I-like Sam-binding...</t>
-  </si>
-  <si>
-    <t>As An Adapter Protein Required</t>
-  </si>
-  <si>
     <t>DEAD box helicase family</t>
   </si>
   <si>
-    <t>DNA replication ATP-dependent helicase...</t>
-  </si>
-  <si>
     <t>Peptidase M23B Family</t>
   </si>
   <si>
-    <t>Adaptor Protein Complex 2 (ap-2).</t>
-  </si>
-  <si>
-    <t>DNA-damage inducible protein DDI1-like...</t>
-  </si>
-  <si>
     <t>NOSIC (NUC001) domain</t>
   </si>
   <si>
@@ -1321,9 +1078,6 @@
     <t>Diphthamine biosynthesis 6</t>
   </si>
   <si>
-    <t>2H phosphoesterase superfamily.</t>
-  </si>
-  <si>
     <t>Asparaginase</t>
   </si>
   <si>
@@ -1339,9 +1093,6 @@
     <t>Leucine-rich repeat</t>
   </si>
   <si>
-    <t>TIGRFAM ribosomal-protein-alanine...</t>
-  </si>
-  <si>
     <t>Geranylgeranyl Transferase Type-2 Subunit</t>
   </si>
   <si>
@@ -1366,9 +1117,6 @@
     <t>Dynactin p62 family</t>
   </si>
   <si>
-    <t>Sodium Neurotransmitter Symporter (snf)...</t>
-  </si>
-  <si>
     <t>E3 UFM1-protein ligase 1 homolog</t>
   </si>
   <si>
@@ -1411,18 +1159,12 @@
     <t>Metallocarboxypeptidase Activity.</t>
   </si>
   <si>
-    <t>TRAFAC class myosin-kinesin ATPase...</t>
-  </si>
-  <si>
     <t>Major role in the synthesis</t>
   </si>
   <si>
     <t>Histone H2A deubiquitinase</t>
   </si>
   <si>
-    <t>Transmembrane emp24 domain-containing...</t>
-  </si>
-  <si>
     <t>SUI1 family</t>
   </si>
   <si>
@@ -1459,9 +1201,6 @@
     <t>HDAC</t>
   </si>
   <si>
-    <t>Protein-glutamine...</t>
-  </si>
-  <si>
     <t>Transmembrane protein 106B</t>
   </si>
   <si>
@@ -1474,15 +1213,9 @@
     <t>RAB19, member RAS oncogene family</t>
   </si>
   <si>
-    <t>Catalyzes the interconversion of...</t>
-  </si>
-  <si>
     <t>Cell-matrix Adhesion</t>
   </si>
   <si>
-    <t>In complex with MON1, is</t>
-  </si>
-  <si>
     <t>U2 snRNA binding</t>
   </si>
   <si>
@@ -1495,18 +1228,9 @@
     <t>Endonuclease Activity</t>
   </si>
   <si>
-    <t>Fibronectin type-III domain-containing...</t>
-  </si>
-  <si>
-    <t>Positive Regulation of Protein...</t>
-  </si>
-  <si>
     <t>Centromere Complex Assembly</t>
   </si>
   <si>
-    <t>Microtubule Interacting and Trafficking...</t>
-  </si>
-  <si>
     <t>Anaphase-promoting complex subunit 4 WD40</t>
   </si>
   <si>
@@ -1549,18 +1273,12 @@
     <t>Iron-storage protein</t>
   </si>
   <si>
-    <t>Possesses two activities a DNA</t>
-  </si>
-  <si>
     <t>Single-stranded Telomeric DNA Binding</t>
   </si>
   <si>
     <t>PFAM PBS lyase HEAT-like repeat</t>
   </si>
   <si>
-    <t>Negative Regulation of Protein...</t>
-  </si>
-  <si>
     <t>ATP-dependent carboxylate-amine ligase</t>
   </si>
   <si>
@@ -1663,9 +1381,6 @@
     <t>ATP-dependent DNA helicase mph1</t>
   </si>
   <si>
-    <t>Adds a GMP to the</t>
-  </si>
-  <si>
     <t>Ras-like Small</t>
   </si>
   <si>
@@ -1681,15 +1396,6 @@
     <t>U3 small nucleolar RNA-associated protein</t>
   </si>
   <si>
-    <t>Involved in targeting and insertion</t>
-  </si>
-  <si>
-    <t>Leucine-rich Repeat-containing Protein...</t>
-  </si>
-  <si>
-    <t>Adds a myristoyl group to</t>
-  </si>
-  <si>
     <t>RAB15, member RAS oncogene family</t>
   </si>
   <si>
@@ -1708,21 +1414,12 @@
     <t>Zinc finger SWIM domain protein</t>
   </si>
   <si>
-    <t>Produces ATP from ADP in</t>
-  </si>
-  <si>
-    <t>D-fructose-1,6-bisphosphate...</t>
-  </si>
-  <si>
     <t>Catalyzes the irreversible cleavage of</t>
   </si>
   <si>
     <t>Cytochrome c oxidase is the</t>
   </si>
   <si>
-    <t>Catalyzes the hydroxylation of...</t>
-  </si>
-  <si>
     <t>Dynamin GTPase effector domain</t>
   </si>
   <si>
@@ -1750,9 +1447,6 @@
     <t>Over Those Bearing Complex Type</t>
   </si>
   <si>
-    <t>Serine threonine tyrosine interacting...</t>
-  </si>
-  <si>
     <t>Transcription factor</t>
   </si>
   <si>
@@ -1765,30 +1459,9 @@
     <t>Eukaryotic Ribosomal Protein El14 Family</t>
   </si>
   <si>
-    <t>Involved in the binding of</t>
-  </si>
-  <si>
-    <t>Serine threonine-protein kinase...</t>
-  </si>
-  <si>
-    <t>Catalyzes the attachment of serine</t>
-  </si>
-  <si>
-    <t>Requires NTP and Is Optimal</t>
-  </si>
-  <si>
     <t>Response regulator aspartate phosphatase</t>
   </si>
   <si>
-    <t>Small Gtpases Rab Are Key</t>
-  </si>
-  <si>
-    <t>LDH MDH superfamily.</t>
-  </si>
-  <si>
-    <t>Hydroxymethylglutaryl-CoA reductase,...</t>
-  </si>
-  <si>
     <t>ADP-ribosylation factor-like protein 8A</t>
   </si>
   <si>
@@ -1867,9 +1540,6 @@
     <t>Stress-induced-phosphoprotein 1</t>
   </si>
   <si>
-    <t>Thyrotropin-releasing Hormone Receptor...</t>
-  </si>
-  <si>
     <t>Immunoglobulin</t>
   </si>
   <si>
@@ -1879,9 +1549,6 @@
     <t>Phosphatase Activity</t>
   </si>
   <si>
-    <t>Protein phosphatase 2A homologues,...</t>
-  </si>
-  <si>
     <t>Ras proteins bind GDP GTP</t>
   </si>
   <si>
@@ -1897,9 +1564,6 @@
     <t>Double-stranded DNA Binding</t>
   </si>
   <si>
-    <t>Catalyzes the ATP-dependent...</t>
-  </si>
-  <si>
     <t>Ribosomal stalk protein</t>
   </si>
   <si>
@@ -1907,6 +1571,342 @@
   </si>
   <si>
     <t>Supplementary Table 14 | ESP short names in Asgard archaea: aggregated genome detection counts before and after decontamination and corresponding loss rates</t>
+  </si>
+  <si>
+    <t>GT (DXD motif)</t>
+  </si>
+  <si>
+    <t>PTRHD1</t>
+  </si>
+  <si>
+    <t>HAD hydrolase (IB, PSP-like)</t>
+  </si>
+  <si>
+    <t>HAD hydrolase (type 3)</t>
+  </si>
+  <si>
+    <t>Viperin (RSAD2)</t>
+  </si>
+  <si>
+    <t>DUSP (N-terminal)</t>
+  </si>
+  <si>
+    <t>VPS28</t>
+  </si>
+  <si>
+    <t>HAMP domain protein</t>
+  </si>
+  <si>
+    <t>Predicted nucleotide-binding domain family</t>
+  </si>
+  <si>
+    <t>DUF2347</t>
+  </si>
+  <si>
+    <t>TRAPα</t>
+  </si>
+  <si>
+    <t>Zinc metalloprotease</t>
+  </si>
+  <si>
+    <t>CheF</t>
+  </si>
+  <si>
+    <t>TMED1</t>
+  </si>
+  <si>
+    <t>CaMKIIδ</t>
+  </si>
+  <si>
+    <t>LEA14 homolog</t>
+  </si>
+  <si>
+    <t>SAM-dependent RNA methyltransferase</t>
+  </si>
+  <si>
+    <t>Brix domain protein</t>
+  </si>
+  <si>
+    <t>EF-G</t>
+  </si>
+  <si>
+    <t>UBAC1</t>
+  </si>
+  <si>
+    <t>PMI (type 2)</t>
+  </si>
+  <si>
+    <t>SPO11 homolog</t>
+  </si>
+  <si>
+    <t>CAND1</t>
+  </si>
+  <si>
+    <t>Raffinose synthase-like</t>
+  </si>
+  <si>
+    <t>MON1</t>
+  </si>
+  <si>
+    <t>Ser/Thr phosphatase</t>
+  </si>
+  <si>
+    <t>LRR C-terminal domain protein</t>
+  </si>
+  <si>
+    <t>GlcNAc transferase</t>
+  </si>
+  <si>
+    <t>TRAPPC1</t>
+  </si>
+  <si>
+    <t>PNGase</t>
+  </si>
+  <si>
+    <t>YaeF/YiiX (C92)</t>
+  </si>
+  <si>
+    <t>INSIG</t>
+  </si>
+  <si>
+    <t>RPE membrane protein</t>
+  </si>
+  <si>
+    <t>FEN1</t>
+  </si>
+  <si>
+    <t>COPII coat protein</t>
+  </si>
+  <si>
+    <t>PIG-M</t>
+  </si>
+  <si>
+    <t>EXT / Exostosin</t>
+  </si>
+  <si>
+    <t>HDAC / Deacetylase (COG0123)</t>
+  </si>
+  <si>
+    <t>Left–right asymmetry factor</t>
+  </si>
+  <si>
+    <t>TYW3</t>
+  </si>
+  <si>
+    <t>Glyoxalase</t>
+  </si>
+  <si>
+    <t>Complex III subunit</t>
+  </si>
+  <si>
+    <t>PGF₂α synthase / Arabinose DH</t>
+  </si>
+  <si>
+    <t>Nuclear receptor coactivator</t>
+  </si>
+  <si>
+    <t>Secretory pathway negative regulator</t>
+  </si>
+  <si>
+    <t>Neutral ceramidase</t>
+  </si>
+  <si>
+    <t>PPP6R3</t>
+  </si>
+  <si>
+    <t>RsmB / NOP2</t>
+  </si>
+  <si>
+    <t>DNA2 helicase/nuclease</t>
+  </si>
+  <si>
+    <t>DDI1-like</t>
+  </si>
+  <si>
+    <t>RimI</t>
+  </si>
+  <si>
+    <t>NSS / SNF transporter</t>
+  </si>
+  <si>
+    <t>Myosin</t>
+  </si>
+  <si>
+    <t>Transglutaminase</t>
+  </si>
+  <si>
+    <t>MtnA / MRI1</t>
+  </si>
+  <si>
+    <t>CCZ1</t>
+  </si>
+  <si>
+    <t>FNDC3A</t>
+  </si>
+  <si>
+    <t>Protein dephosphorylation positive regulator</t>
+  </si>
+  <si>
+    <t>MIT domain</t>
+  </si>
+  <si>
+    <t>Ubiquitination negative regulator</t>
+  </si>
+  <si>
+    <t>LRR protein</t>
+  </si>
+  <si>
+    <t>FBPase</t>
+  </si>
+  <si>
+    <t>ATP synthase α subunit</t>
+  </si>
+  <si>
+    <t>KMO</t>
+  </si>
+  <si>
+    <t>STYX</t>
+  </si>
+  <si>
+    <t>STK11IP</t>
+  </si>
+  <si>
+    <t>tRNA–ribosome binding factor</t>
+  </si>
+  <si>
+    <t>HMGCR</t>
+  </si>
+  <si>
+    <t>TRH receptor–binding protein</t>
+  </si>
+  <si>
+    <t>PP2A catalytic domain</t>
+  </si>
+  <si>
+    <t>KdkA</t>
+  </si>
+  <si>
+    <t>Histone-like protein HU</t>
+  </si>
+  <si>
+    <t>ITGA3</t>
+  </si>
+  <si>
+    <t>DV patterning factor</t>
+  </si>
+  <si>
+    <t>30S assembly factor</t>
+  </si>
+  <si>
+    <t>Acetate/succinate transporter</t>
+  </si>
+  <si>
+    <t>Topo I</t>
+  </si>
+  <si>
+    <t>Genome integrity factor</t>
+  </si>
+  <si>
+    <t>OmcB</t>
+  </si>
+  <si>
+    <t>OB-fold tRNA helicase</t>
+  </si>
+  <si>
+    <t>TMED/p24</t>
+  </si>
+  <si>
+    <t>Dynein regulator</t>
+  </si>
+  <si>
+    <t>CapZ</t>
+  </si>
+  <si>
+    <t>Multi-copy unassigned gene</t>
+  </si>
+  <si>
+    <t>Claudin</t>
+  </si>
+  <si>
+    <t>Exocyst subunit</t>
+  </si>
+  <si>
+    <t>EF-Tu</t>
+  </si>
+  <si>
+    <t>ITGB1</t>
+  </si>
+  <si>
+    <t>Muscle cytoskeleton regulator</t>
+  </si>
+  <si>
+    <t>Ribosome biogenesis factor</t>
+  </si>
+  <si>
+    <t>Nitrate/nitrite transporter</t>
+  </si>
+  <si>
+    <t>eRF1 / RF1</t>
+  </si>
+  <si>
+    <t>tRNA pseudouridine synthase</t>
+  </si>
+  <si>
+    <t>Pyrophosphatase</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L14</t>
+  </si>
+  <si>
+    <t>PhpP</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L24</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L1</t>
+  </si>
+  <si>
+    <t>Phytol kinase</t>
+  </si>
+  <si>
+    <t>Villin</t>
+  </si>
+  <si>
+    <t>Tissue factor</t>
+  </si>
+  <si>
+    <t>Mff</t>
+  </si>
+  <si>
+    <t>AP-2 subunit</t>
+  </si>
+  <si>
+    <t>2H phosphoesterase superfamily</t>
+  </si>
+  <si>
+    <t>Replicative DNA polymerase</t>
+  </si>
+  <si>
+    <t>tRNAᴴⁱˢ guanyltransferase</t>
+  </si>
+  <si>
+    <t>FtsY</t>
+  </si>
+  <si>
+    <t>N-myristoyltransferase</t>
+  </si>
+  <si>
+    <t>Seryl-tRNA synthetase</t>
+  </si>
+  <si>
+    <t>Poly(A) polymerase</t>
+  </si>
+  <si>
+    <t>LDH MDH superfamily</t>
+  </si>
+  <si>
+    <t>Rab11</t>
   </si>
 </sst>
 </file>
@@ -2279,7 +2279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D627"/>
+  <dimension ref="A1:D629"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="39" style="1" customWidth="1"/>
@@ -2291,7 +2291,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>628</v>
+        <v>516</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -2548,7 +2548,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>517</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1">
         <v>22</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="1">
         <v>30</v>
@@ -2604,7 +2604,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" s="1">
         <v>10</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" s="1">
         <v>5</v>
@@ -2632,7 +2632,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" s="1">
         <v>4</v>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="1">
         <v>7</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>518</v>
       </c>
       <c r="B28" s="1">
         <v>2</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1">
         <v>2</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1">
         <v>2</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>626</v>
+        <v>514</v>
       </c>
       <c r="B31" s="1">
         <v>2</v>
@@ -2716,7 +2716,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1">
         <v>2</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1">
         <v>5</v>
@@ -2744,7 +2744,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>627</v>
+        <v>515</v>
       </c>
       <c r="B34" s="1">
         <v>2</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B35" s="1">
         <v>3</v>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B36" s="1">
         <v>13</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" s="1">
         <v>6</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1">
         <v>6</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>519</v>
       </c>
       <c r="B39" s="1">
         <v>6</v>
@@ -2828,7 +2828,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B40" s="1">
         <v>3</v>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B41" s="1">
         <v>3</v>
@@ -2856,7 +2856,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B42" s="1">
         <v>3</v>
@@ -2870,7 +2870,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B43" s="1">
         <v>3</v>
@@ -2884,7 +2884,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B44" s="1">
         <v>18</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B45" s="1">
         <v>3</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B46" s="1">
         <v>10</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B47" s="1">
         <v>3</v>
@@ -2940,7 +2940,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B48" s="1">
         <v>3</v>
@@ -2954,7 +2954,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>520</v>
       </c>
       <c r="B49" s="1">
         <v>12</v>
@@ -2968,7 +2968,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B50" s="1">
         <v>4</v>
@@ -2982,7 +2982,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B51" s="1">
         <v>5</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B52" s="1">
         <v>4</v>
@@ -3010,7 +3010,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B53" s="1">
         <v>8</v>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B54" s="1">
         <v>8</v>
@@ -3038,7 +3038,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B55" s="1">
         <v>10</v>
@@ -3052,7 +3052,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B56" s="1">
         <v>5</v>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B57" s="1">
         <v>5</v>
@@ -3080,7 +3080,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B58" s="1">
         <v>16</v>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B59" s="1">
         <v>6</v>
@@ -3108,7 +3108,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B60" s="1">
         <v>6</v>
@@ -3122,7 +3122,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B61" s="1">
         <v>14</v>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B62" s="1">
         <v>26</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>62</v>
+        <v>588</v>
       </c>
       <c r="B63" s="1">
         <v>70</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>63</v>
+        <v>589</v>
       </c>
       <c r="B64" s="1">
         <v>19</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B65" s="1">
         <v>23</v>
@@ -3192,7 +3192,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B66" s="1">
         <v>28</v>
@@ -3206,7 +3206,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B67" s="1">
         <v>26</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B68" s="1">
         <v>26</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B69" s="1">
         <v>9</v>
@@ -3248,7 +3248,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B70" s="1">
         <v>9</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>70</v>
+        <v>590</v>
       </c>
       <c r="B71" s="1">
         <v>61</v>
@@ -3276,7 +3276,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>71</v>
+        <v>521</v>
       </c>
       <c r="B72" s="1">
         <v>10</v>
@@ -3290,7 +3290,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B73" s="1">
         <v>12</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B74" s="1">
         <v>65</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B75" s="1">
         <v>11</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B76" s="1">
         <v>12</v>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B77" s="1">
         <v>13</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B78" s="1">
         <v>43</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B79" s="1">
         <v>14</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B80" s="1">
         <v>29</v>
@@ -3402,7 +3402,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B81" s="1">
         <v>20</v>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B82" s="1">
         <v>30</v>
@@ -3430,7 +3430,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B83" s="1">
         <v>63</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B84" s="1">
         <v>35</v>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B85" s="1">
         <v>37</v>
@@ -3472,7 +3472,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B86" s="1">
         <v>44</v>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B87" s="1">
         <v>46</v>
@@ -3500,7 +3500,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B88" s="1">
         <v>100</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B89" s="1">
         <v>57</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B90" s="1">
         <v>372</v>
@@ -3542,7 +3542,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B91" s="1">
         <v>363</v>
@@ -3556,7 +3556,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>91</v>
+        <v>522</v>
       </c>
       <c r="B92" s="1">
         <v>281</v>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B93" s="1">
         <v>366</v>
@@ -3584,7 +3584,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B94" s="1">
         <v>362</v>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B95" s="1">
         <v>303</v>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B96" s="1">
         <v>300</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
-        <v>96</v>
+        <v>591</v>
       </c>
       <c r="B97" s="1">
         <v>214</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B98" s="1">
         <v>190</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B99" s="1">
         <v>405</v>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>99</v>
+        <v>523</v>
       </c>
       <c r="B100" s="1">
         <v>146</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B101" s="1">
         <v>128</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B102" s="1">
         <v>125</v>
@@ -3710,7 +3710,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B103" s="1">
         <v>121</v>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B104" s="1">
         <v>212</v>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B105" s="1">
         <v>114</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B106" s="1">
         <v>115</v>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B107" s="1">
         <v>93</v>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B108" s="1">
         <v>88</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B109" s="1">
         <v>80</v>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B110" s="1">
         <v>71</v>
@@ -3822,7 +3822,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>110</v>
+        <v>592</v>
       </c>
       <c r="B111" s="1">
         <v>68</v>
@@ -3836,7 +3836,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>111</v>
+        <v>524</v>
       </c>
       <c r="B112" s="1">
         <v>66</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B113" s="1">
         <v>64</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>113</v>
+        <v>593</v>
       </c>
       <c r="B114" s="1">
         <v>63</v>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B115" s="1">
         <v>86</v>
@@ -3892,7 +3892,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B116" s="1">
         <v>56</v>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="B117" s="1">
         <v>87</v>
@@ -3920,7 +3920,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B118" s="1">
         <v>53</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="B119" s="1">
         <v>51</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
-        <v>119</v>
+        <v>594</v>
       </c>
       <c r="B120" s="1">
         <v>51</v>
@@ -3962,7 +3962,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B121" s="1">
         <v>46</v>
@@ -3976,7 +3976,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B122" s="1">
         <v>59</v>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B123" s="1">
         <v>39</v>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A124" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B124" s="1">
         <v>136</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A125" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B125" s="1">
         <v>46</v>
@@ -4032,7 +4032,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A126" s="1" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B126" s="1">
         <v>35</v>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A127" s="1" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B127" s="1">
         <v>35</v>
@@ -4060,7 +4060,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A128" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B128" s="1">
         <v>35</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B129" s="1">
         <v>35</v>
@@ -4088,7 +4088,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B130" s="1">
         <v>33</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A131" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B131" s="1">
         <v>37</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A132" s="1" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B132" s="1">
         <v>32</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A133" s="1" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B133" s="1">
         <v>31</v>
@@ -4144,7 +4144,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A134" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B134" s="1">
         <v>30</v>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A135" s="1" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B135" s="1">
         <v>29</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A136" s="1" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B136" s="1">
         <v>29</v>
@@ -4186,7 +4186,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A137" s="1" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B137" s="1">
         <v>28</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A138" s="1" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="B138" s="1">
         <v>28</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A139" s="1" t="s">
-        <v>138</v>
+        <v>525</v>
       </c>
       <c r="B139" s="1">
         <v>27</v>
@@ -4228,7 +4228,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A140" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="B140" s="1">
         <v>26</v>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A141" s="1" t="s">
-        <v>140</v>
+        <v>526</v>
       </c>
       <c r="B141" s="1">
         <v>43</v>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="B142" s="1">
         <v>25</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A143" s="1" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="B143" s="1">
         <v>25</v>
@@ -4284,7 +4284,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="B144" s="1">
         <v>49</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A145" s="1" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B145" s="1">
         <v>23</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="B146" s="1">
         <v>23</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="B147" s="1">
         <v>23</v>
@@ -4340,7 +4340,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B148" s="1">
         <v>22</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B149" s="1">
         <v>42</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A150" s="1" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B150" s="1">
         <v>26</v>
@@ -4382,7 +4382,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A151" s="1" t="s">
-        <v>150</v>
+        <v>595</v>
       </c>
       <c r="B151" s="1">
         <v>24</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A152" s="1" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="B152" s="1">
         <v>21</v>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A153" s="1" t="s">
-        <v>152</v>
+        <v>596</v>
       </c>
       <c r="B153" s="1">
         <v>31</v>
@@ -4424,7 +4424,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A154" s="1" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="B154" s="1">
         <v>36</v>
@@ -4438,7 +4438,7 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A155" s="1" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="B155" s="1">
         <v>25</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A156" s="1" t="s">
-        <v>155</v>
+        <v>527</v>
       </c>
       <c r="B156" s="1">
         <v>29</v>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A157" s="1" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="B157" s="1">
         <v>19</v>
@@ -4480,7 +4480,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A158" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="B158" s="1">
         <v>29</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A159" s="1" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="B159" s="1">
         <v>18</v>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A160" s="1" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="B160" s="1">
         <v>18</v>
@@ -4522,7 +4522,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A161" s="1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B161" s="1">
         <v>18</v>
@@ -4536,7 +4536,7 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A162" s="1" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="B162" s="1">
         <v>18</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A163" s="1" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B163" s="1">
         <v>18</v>
@@ -4564,7 +4564,7 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A164" s="1" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="B164" s="1">
         <v>18</v>
@@ -4578,7 +4578,7 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A165" s="1" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="B165" s="1">
         <v>18</v>
@@ -4592,7 +4592,7 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A166" s="1" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="B166" s="1">
         <v>19</v>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A167" s="1" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B167" s="1">
         <v>16</v>
@@ -4620,7 +4620,7 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A168" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="B168" s="1">
         <v>16</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A169" s="1" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B169" s="1">
         <v>16</v>
@@ -4648,7 +4648,7 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A170" s="1" t="s">
-        <v>169</v>
+        <v>528</v>
       </c>
       <c r="B170" s="1">
         <v>16</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A171" s="1" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B171" s="1">
         <v>16</v>
@@ -4676,7 +4676,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A172" s="1" t="s">
-        <v>171</v>
+        <v>529</v>
       </c>
       <c r="B172" s="1">
         <v>16</v>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A173" s="1" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B173" s="1">
         <v>16</v>
@@ -4704,7 +4704,7 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A174" s="1" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="B174" s="1">
         <v>15</v>
@@ -4718,7 +4718,7 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A175" s="1" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="B175" s="1">
         <v>15</v>
@@ -4732,7 +4732,7 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A176" s="1" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="B176" s="1">
         <v>20</v>
@@ -4746,7 +4746,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A177" s="1" t="s">
-        <v>176</v>
+        <v>597</v>
       </c>
       <c r="B177" s="1">
         <v>24</v>
@@ -4760,7 +4760,7 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A178" s="1" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B178" s="1">
         <v>16</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A179" s="1" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B179" s="1">
         <v>19</v>
@@ -4788,7 +4788,7 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A180" s="1" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="B180" s="1">
         <v>14</v>
@@ -4802,7 +4802,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A181" s="1" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="B181" s="1">
         <v>14</v>
@@ -4816,7 +4816,7 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A182" s="1" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="B182" s="1">
         <v>14</v>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A183" s="1" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B183" s="1">
         <v>14</v>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A184" s="1" t="s">
-        <v>183</v>
+        <v>530</v>
       </c>
       <c r="B184" s="1">
         <v>23</v>
@@ -4858,7 +4858,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A185" s="1" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="B185" s="1">
         <v>14</v>
@@ -4872,7 +4872,7 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A186" s="1" t="s">
-        <v>185</v>
+        <v>598</v>
       </c>
       <c r="B186" s="1">
         <v>14</v>
@@ -4886,7 +4886,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A187" s="1" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="B187" s="1">
         <v>25</v>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A188" s="1" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="B188" s="1">
         <v>14</v>
@@ -4914,7 +4914,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A189" s="1" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="B189" s="1">
         <v>13</v>
@@ -4928,7 +4928,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A190" s="1" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="B190" s="1">
         <v>13</v>
@@ -4942,7 +4942,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A191" s="1" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="B191" s="1">
         <v>13</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A192" s="1" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="B192" s="1">
         <v>13</v>
@@ -4970,7 +4970,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A193" s="1" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="B193" s="1">
         <v>14</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A194" s="1" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="B194" s="1">
         <v>13</v>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A195" s="1" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="B195" s="1">
         <v>12</v>
@@ -5012,7 +5012,7 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A196" s="1" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="B196" s="1">
         <v>13</v>
@@ -5026,7 +5026,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A197" s="1" t="s">
-        <v>196</v>
+        <v>531</v>
       </c>
       <c r="B197" s="1">
         <v>11</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A198" s="1" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="B198" s="1">
         <v>11</v>
@@ -5054,7 +5054,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A199" s="1" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="B199" s="1">
         <v>11</v>
@@ -5068,7 +5068,7 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A200" s="1" t="s">
-        <v>199</v>
+        <v>532</v>
       </c>
       <c r="B200" s="1">
         <v>11</v>
@@ -5082,7 +5082,7 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A201" s="1" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="B201" s="1">
         <v>12</v>
@@ -5096,7 +5096,7 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A202" s="1" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="B202" s="1">
         <v>19</v>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A203" s="1" t="s">
-        <v>202</v>
+        <v>533</v>
       </c>
       <c r="B203" s="1">
         <v>11</v>
@@ -5124,7 +5124,7 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A204" s="1" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="B204" s="1">
         <v>10</v>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A205" s="1" t="s">
-        <v>204</v>
+        <v>534</v>
       </c>
       <c r="B205" s="1">
         <v>12</v>
@@ -5152,7 +5152,7 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A206" s="1" t="s">
-        <v>205</v>
+        <v>535</v>
       </c>
       <c r="B206" s="1">
         <v>20</v>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A207" s="1" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="B207" s="1">
         <v>10</v>
@@ -5180,7 +5180,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A208" s="1" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="B208" s="1">
         <v>11</v>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A209" s="1" t="s">
-        <v>208</v>
+        <v>536</v>
       </c>
       <c r="B209" s="1">
         <v>10</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A210" s="1" t="s">
-        <v>209</v>
+        <v>599</v>
       </c>
       <c r="B210" s="1">
         <v>10</v>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A211" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="B211" s="1">
         <v>61</v>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A212" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="B212" s="1">
         <v>9</v>
@@ -5250,7 +5250,7 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A213" s="1" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="B213" s="1">
         <v>9</v>
@@ -5264,7 +5264,7 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A214" s="1" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="B214" s="1">
         <v>9</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A215" s="1" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="B215" s="1">
         <v>10</v>
@@ -5292,7 +5292,7 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A216" s="1" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="B216" s="1">
         <v>9</v>
@@ -5306,7 +5306,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A217" s="1" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="B217" s="1">
         <v>9</v>
@@ -5320,7 +5320,7 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A218" s="1" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="B218" s="1">
         <v>9</v>
@@ -5334,7 +5334,7 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A219" s="1" t="s">
-        <v>218</v>
+        <v>600</v>
       </c>
       <c r="B219" s="1">
         <v>8</v>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A220" s="1" t="s">
-        <v>219</v>
+        <v>601</v>
       </c>
       <c r="B220" s="1">
         <v>8</v>
@@ -5362,7 +5362,7 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A221" s="1" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="B221" s="1">
         <v>8</v>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A222" s="1" t="s">
-        <v>221</v>
+        <v>602</v>
       </c>
       <c r="B222" s="1">
         <v>14</v>
@@ -5390,7 +5390,7 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A223" s="1" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="B223" s="1">
         <v>8</v>
@@ -5404,7 +5404,7 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A224" s="1" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="B224" s="1">
         <v>8</v>
@@ -5418,7 +5418,7 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A225" s="1" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="B225" s="1">
         <v>8</v>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A226" s="1" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="B226" s="1">
         <v>8</v>
@@ -5446,7 +5446,7 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A227" s="1" t="s">
-        <v>226</v>
+        <v>537</v>
       </c>
       <c r="B227" s="1">
         <v>8</v>
@@ -5460,7 +5460,7 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A228" s="1" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="B228" s="1">
         <v>8</v>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A229" s="1" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="B229" s="1">
         <v>9</v>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A230" s="1" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="B230" s="1">
         <v>10</v>
@@ -5502,7 +5502,7 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A231" s="1" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="B231" s="1">
         <v>7</v>
@@ -5516,7 +5516,7 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A232" s="1" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="B232" s="1">
         <v>7</v>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A233" s="1" t="s">
-        <v>232</v>
+        <v>538</v>
       </c>
       <c r="B233" s="1">
         <v>7</v>
@@ -5544,7 +5544,7 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A234" s="1" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B234" s="1">
         <v>8</v>
@@ -5558,7 +5558,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A235" s="1" t="s">
-        <v>234</v>
+        <v>539</v>
       </c>
       <c r="B235" s="1">
         <v>9</v>
@@ -5572,7 +5572,7 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A236" s="1" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="B236" s="1">
         <v>7</v>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A237" s="1" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="B237" s="1">
         <v>7</v>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A238" s="1" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="B238" s="1">
         <v>7</v>
@@ -5614,7 +5614,7 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A239" s="1" t="s">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="B239" s="1">
         <v>9</v>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A240" s="1" t="s">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="B240" s="1">
         <v>7</v>
@@ -5642,7 +5642,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A241" s="1" t="s">
-        <v>240</v>
+        <v>202</v>
       </c>
       <c r="B241" s="1">
         <v>7</v>
@@ -5656,7 +5656,7 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A242" s="1" t="s">
-        <v>241</v>
+        <v>203</v>
       </c>
       <c r="B242" s="1">
         <v>7</v>
@@ -5670,7 +5670,7 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A243" s="1" t="s">
-        <v>242</v>
+        <v>540</v>
       </c>
       <c r="B243" s="1">
         <v>7</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A244" s="1" t="s">
-        <v>243</v>
+        <v>541</v>
       </c>
       <c r="B244" s="1">
         <v>9</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A245" s="1" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="B245" s="1">
         <v>7</v>
@@ -5712,7 +5712,7 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A246" s="1" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="B246" s="1">
         <v>7</v>
@@ -5726,7 +5726,7 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A247" s="1" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="B247" s="1">
         <v>7</v>
@@ -5740,7 +5740,7 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A248" s="1" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="B248" s="1">
         <v>15</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A249" s="1" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="B249" s="1">
         <v>7</v>
@@ -5768,7 +5768,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A250" s="1" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="B250" s="1">
         <v>6</v>
@@ -5782,7 +5782,7 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A251" s="1" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="B251" s="1">
         <v>6</v>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A252" s="1" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="B252" s="1">
         <v>6</v>
@@ -5810,7 +5810,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A253" s="1" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="B253" s="1">
         <v>6</v>
@@ -5824,7 +5824,7 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A254" s="1" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="B254" s="1">
         <v>16</v>
@@ -5838,7 +5838,7 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A255" s="1" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="B255" s="1">
         <v>6</v>
@@ -5852,7 +5852,7 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A256" s="1" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="B256" s="1">
         <v>6</v>
@@ -5866,7 +5866,7 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A257" s="1" t="s">
-        <v>256</v>
+        <v>542</v>
       </c>
       <c r="B257" s="1">
         <v>6</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A258" s="1" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="B258" s="1">
         <v>6</v>
@@ -5894,7 +5894,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A259" s="1" t="s">
-        <v>258</v>
+        <v>217</v>
       </c>
       <c r="B259" s="1">
         <v>6</v>
@@ -5908,7 +5908,7 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A260" s="1" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="B260" s="1">
         <v>6</v>
@@ -5922,7 +5922,7 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A261" s="1" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="B261" s="1">
         <v>6</v>
@@ -5936,7 +5936,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A262" s="1" t="s">
-        <v>261</v>
+        <v>543</v>
       </c>
       <c r="B262" s="1">
         <v>8</v>
@@ -5950,7 +5950,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A263" s="1" t="s">
-        <v>262</v>
+        <v>544</v>
       </c>
       <c r="B263" s="1">
         <v>6</v>
@@ -5964,7 +5964,7 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A264" s="1" t="s">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="B264" s="1">
         <v>6</v>
@@ -5978,7 +5978,7 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A265" s="1" t="s">
-        <v>264</v>
+        <v>545</v>
       </c>
       <c r="B265" s="1">
         <v>7</v>
@@ -5992,7 +5992,7 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A266" s="1" t="s">
-        <v>265</v>
+        <v>546</v>
       </c>
       <c r="B266" s="1">
         <v>6</v>
@@ -6006,7 +6006,7 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A267" s="1" t="s">
-        <v>266</v>
+        <v>221</v>
       </c>
       <c r="B267" s="1">
         <v>5</v>
@@ -6020,7 +6020,7 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A268" s="1" t="s">
-        <v>267</v>
+        <v>222</v>
       </c>
       <c r="B268" s="1">
         <v>5</v>
@@ -6034,7 +6034,7 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A269" s="1" t="s">
-        <v>268</v>
+        <v>223</v>
       </c>
       <c r="B269" s="1">
         <v>8</v>
@@ -6048,7 +6048,7 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A270" s="1" t="s">
-        <v>269</v>
+        <v>224</v>
       </c>
       <c r="B270" s="1">
         <v>7</v>
@@ -6062,7 +6062,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A271" s="1" t="s">
-        <v>270</v>
+        <v>547</v>
       </c>
       <c r="B271" s="1">
         <v>5</v>
@@ -6076,7 +6076,7 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A272" s="1" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="B272" s="1">
         <v>5</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A273" s="1" t="s">
-        <v>272</v>
+        <v>548</v>
       </c>
       <c r="B273" s="1">
         <v>5</v>
@@ -6104,7 +6104,7 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A274" s="1" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="B274" s="1">
         <v>5</v>
@@ -6118,7 +6118,7 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A275" s="1" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
       <c r="B275" s="1">
         <v>5</v>
@@ -6132,7 +6132,7 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A276" s="1" t="s">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="B276" s="1">
         <v>5</v>
@@ -6146,7 +6146,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A277" s="1" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="B277" s="1">
         <v>5</v>
@@ -6160,7 +6160,7 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A278" s="1" t="s">
-        <v>277</v>
+        <v>230</v>
       </c>
       <c r="B278" s="1">
         <v>5</v>
@@ -6174,7 +6174,7 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A279" s="1" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
       <c r="B279" s="1">
         <v>8</v>
@@ -6188,7 +6188,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A280" s="1" t="s">
-        <v>279</v>
+        <v>232</v>
       </c>
       <c r="B280" s="1">
         <v>9</v>
@@ -6202,7 +6202,7 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A281" s="1" t="s">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="B281" s="1">
         <v>5</v>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A282" s="1" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="B282" s="1">
         <v>6</v>
@@ -6230,7 +6230,7 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A283" s="1" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="B283" s="1">
         <v>5</v>
@@ -6244,7 +6244,7 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A284" s="1" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="B284" s="1">
         <v>6</v>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A285" s="1" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="B285" s="1">
         <v>5</v>
@@ -6272,7 +6272,7 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A286" s="1" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="B286" s="1">
         <v>5</v>
@@ -6286,7 +6286,7 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A287" s="1" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="B287" s="1">
         <v>5</v>
@@ -6300,7 +6300,7 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A288" s="1" t="s">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="B288" s="1">
         <v>5</v>
@@ -6314,7 +6314,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A289" s="1" t="s">
-        <v>288</v>
+        <v>241</v>
       </c>
       <c r="B289" s="1">
         <v>5</v>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A290" s="1" t="s">
-        <v>289</v>
+        <v>242</v>
       </c>
       <c r="B290" s="1">
         <v>5</v>
@@ -6342,7 +6342,7 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A291" s="1" t="s">
-        <v>290</v>
+        <v>603</v>
       </c>
       <c r="B291" s="1">
         <v>5</v>
@@ -6356,7 +6356,7 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A292" s="1" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="B292" s="1">
         <v>9</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A293" s="1" t="s">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="B293" s="1">
         <v>4</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A294" s="1" t="s">
-        <v>293</v>
+        <v>549</v>
       </c>
       <c r="B294" s="1">
         <v>4</v>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A295" s="1" t="s">
-        <v>294</v>
+        <v>245</v>
       </c>
       <c r="B295" s="1">
         <v>4</v>
@@ -6412,7 +6412,7 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A296" s="1" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="B296" s="1">
         <v>4</v>
@@ -6426,7 +6426,7 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A297" s="1" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="B297" s="1">
         <v>4</v>
@@ -6440,7 +6440,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A298" s="1" t="s">
-        <v>297</v>
+        <v>248</v>
       </c>
       <c r="B298" s="1">
         <v>4</v>
@@ -6454,7 +6454,7 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A299" s="1" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
       <c r="B299" s="1">
         <v>4</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A300" s="1" t="s">
-        <v>299</v>
+        <v>604</v>
       </c>
       <c r="B300" s="1">
         <v>4</v>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A301" s="1" t="s">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="B301" s="1">
         <v>4</v>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A302" s="1" t="s">
-        <v>301</v>
+        <v>251</v>
       </c>
       <c r="B302" s="1">
         <v>4</v>
@@ -6510,7 +6510,7 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A303" s="1" t="s">
-        <v>302</v>
+        <v>252</v>
       </c>
       <c r="B303" s="1">
         <v>5</v>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A304" s="1" t="s">
-        <v>303</v>
+        <v>253</v>
       </c>
       <c r="B304" s="1">
         <v>7</v>
@@ -6538,7 +6538,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A305" s="1" t="s">
-        <v>304</v>
+        <v>254</v>
       </c>
       <c r="B305" s="1">
         <v>4</v>
@@ -6552,7 +6552,7 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A306" s="1" t="s">
-        <v>305</v>
+        <v>255</v>
       </c>
       <c r="B306" s="1">
         <v>5</v>
@@ -6566,7 +6566,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A307" s="1" t="s">
-        <v>306</v>
+        <v>550</v>
       </c>
       <c r="B307" s="1">
         <v>4</v>
@@ -6580,7 +6580,7 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A308" s="1" t="s">
-        <v>307</v>
+        <v>256</v>
       </c>
       <c r="B308" s="1">
         <v>4</v>
@@ -6594,7 +6594,7 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A309" s="1" t="s">
-        <v>308</v>
+        <v>551</v>
       </c>
       <c r="B309" s="1">
         <v>4</v>
@@ -6608,7 +6608,7 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A310" s="1" t="s">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="B310" s="1">
         <v>7</v>
@@ -6622,7 +6622,7 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A311" s="1" t="s">
-        <v>310</v>
+        <v>258</v>
       </c>
       <c r="B311" s="1">
         <v>4</v>
@@ -6636,7 +6636,7 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A312" s="1" t="s">
-        <v>311</v>
+        <v>259</v>
       </c>
       <c r="B312" s="1">
         <v>11</v>
@@ -6650,7 +6650,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A313" s="1" t="s">
-        <v>312</v>
+        <v>260</v>
       </c>
       <c r="B313" s="1">
         <v>4</v>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A314" s="1" t="s">
-        <v>313</v>
+        <v>261</v>
       </c>
       <c r="B314" s="1">
         <v>4</v>
@@ -6678,7 +6678,7 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A315" s="1" t="s">
-        <v>314</v>
+        <v>262</v>
       </c>
       <c r="B315" s="1">
         <v>5</v>
@@ -6692,7 +6692,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A316" s="1" t="s">
-        <v>315</v>
+        <v>263</v>
       </c>
       <c r="B316" s="1">
         <v>7</v>
@@ -6706,7 +6706,7 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A317" s="1" t="s">
-        <v>316</v>
+        <v>264</v>
       </c>
       <c r="B317" s="1">
         <v>4</v>
@@ -6720,7 +6720,7 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A318" s="1" t="s">
-        <v>317</v>
+        <v>265</v>
       </c>
       <c r="B318" s="1">
         <v>5</v>
@@ -6734,7 +6734,7 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A319" s="1" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
       <c r="B319" s="1">
         <v>4</v>
@@ -6748,7 +6748,7 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A320" s="1" t="s">
-        <v>319</v>
+        <v>267</v>
       </c>
       <c r="B320" s="1">
         <v>4</v>
@@ -6762,7 +6762,7 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A321" s="1" t="s">
-        <v>320</v>
+        <v>268</v>
       </c>
       <c r="B321" s="1">
         <v>6</v>
@@ -6776,7 +6776,7 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A322" s="1" t="s">
-        <v>321</v>
+        <v>269</v>
       </c>
       <c r="B322" s="1">
         <v>4</v>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A323" s="1" t="s">
-        <v>322</v>
+        <v>552</v>
       </c>
       <c r="B323" s="1">
         <v>5</v>
@@ -6804,7 +6804,7 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A324" s="1" t="s">
-        <v>323</v>
+        <v>270</v>
       </c>
       <c r="B324" s="1">
         <v>6</v>
@@ -6818,7 +6818,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A325" s="1" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="B325" s="1">
         <v>8</v>
@@ -6832,13 +6832,13 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A326" s="1" t="s">
-        <v>325</v>
+        <v>606</v>
       </c>
       <c r="B326" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C326" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D326" s="5">
         <v>0</v>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A327" s="1" t="s">
-        <v>326</v>
+        <v>607</v>
       </c>
       <c r="B327" s="1">
         <v>4</v>
@@ -6860,7 +6860,7 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A328" s="1" t="s">
-        <v>327</v>
+        <v>605</v>
       </c>
       <c r="B328" s="1">
         <v>4</v>
@@ -6874,7 +6874,7 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A329" s="1" t="s">
-        <v>328</v>
+        <v>608</v>
       </c>
       <c r="B329" s="1">
         <v>4</v>
@@ -6888,7 +6888,7 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A330" s="1" t="s">
-        <v>329</v>
+        <v>609</v>
       </c>
       <c r="B330" s="1">
         <v>4</v>
@@ -6902,7 +6902,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A331" s="1" t="s">
-        <v>330</v>
+        <v>272</v>
       </c>
       <c r="B331" s="1">
         <v>4</v>
@@ -6916,7 +6916,7 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A332" s="1" t="s">
-        <v>331</v>
+        <v>610</v>
       </c>
       <c r="B332" s="1">
         <v>4</v>
@@ -6930,7 +6930,7 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A333" s="1" t="s">
-        <v>332</v>
+        <v>273</v>
       </c>
       <c r="B333" s="1">
         <v>4</v>
@@ -6944,13 +6944,13 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A334" s="1" t="s">
-        <v>333</v>
+        <v>274</v>
       </c>
       <c r="B334" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C334" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D334" s="5">
         <v>0</v>
@@ -6958,7 +6958,7 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A335" s="1" t="s">
-        <v>334</v>
+        <v>553</v>
       </c>
       <c r="B335" s="1">
         <v>3</v>
@@ -6972,7 +6972,7 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A336" s="1" t="s">
-        <v>335</v>
+        <v>275</v>
       </c>
       <c r="B336" s="1">
         <v>3</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A337" s="1" t="s">
-        <v>336</v>
+        <v>276</v>
       </c>
       <c r="B337" s="1">
         <v>3</v>
@@ -7000,13 +7000,13 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A338" s="1" t="s">
-        <v>337</v>
+        <v>277</v>
       </c>
       <c r="B338" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C338" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D338" s="5">
         <v>0</v>
@@ -7014,13 +7014,13 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A339" s="1" t="s">
-        <v>338</v>
+        <v>278</v>
       </c>
       <c r="B339" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C339" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D339" s="5">
         <v>0</v>
@@ -7028,7 +7028,7 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A340" s="1" t="s">
-        <v>339</v>
+        <v>279</v>
       </c>
       <c r="B340" s="1">
         <v>3</v>
@@ -7042,13 +7042,13 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A341" s="1" t="s">
-        <v>340</v>
+        <v>280</v>
       </c>
       <c r="B341" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C341" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D341" s="5">
         <v>0</v>
@@ -7056,13 +7056,13 @@
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A342" s="1" t="s">
-        <v>341</v>
+        <v>281</v>
       </c>
       <c r="B342" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C342" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D342" s="5">
         <v>0</v>
@@ -7070,7 +7070,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A343" s="1" t="s">
-        <v>342</v>
+        <v>282</v>
       </c>
       <c r="B343" s="1">
         <v>3</v>
@@ -7084,7 +7084,7 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A344" s="1" t="s">
-        <v>343</v>
+        <v>283</v>
       </c>
       <c r="B344" s="1">
         <v>3</v>
@@ -7098,7 +7098,7 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A345" s="1" t="s">
-        <v>344</v>
+        <v>284</v>
       </c>
       <c r="B345" s="1">
         <v>3</v>
@@ -7112,7 +7112,7 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A346" s="1" t="s">
-        <v>345</v>
+        <v>554</v>
       </c>
       <c r="B346" s="1">
         <v>3</v>
@@ -7126,13 +7126,13 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A347" s="1" t="s">
-        <v>346</v>
+        <v>285</v>
       </c>
       <c r="B347" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C347" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D347" s="5">
         <v>0</v>
@@ -7140,13 +7140,13 @@
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A348" s="1" t="s">
-        <v>347</v>
+        <v>286</v>
       </c>
       <c r="B348" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C348" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D348" s="5">
         <v>0</v>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A349" s="1" t="s">
-        <v>348</v>
+        <v>287</v>
       </c>
       <c r="B349" s="1">
         <v>3</v>
@@ -7168,7 +7168,7 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A350" s="1" t="s">
-        <v>349</v>
+        <v>288</v>
       </c>
       <c r="B350" s="1">
         <v>3</v>
@@ -7182,7 +7182,7 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A351" s="1" t="s">
-        <v>350</v>
+        <v>555</v>
       </c>
       <c r="B351" s="1">
         <v>3</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A352" s="1" t="s">
-        <v>351</v>
+        <v>289</v>
       </c>
       <c r="B352" s="1">
         <v>3</v>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A353" s="1" t="s">
-        <v>352</v>
+        <v>556</v>
       </c>
       <c r="B353" s="1">
         <v>3</v>
@@ -7224,13 +7224,13 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A354" s="1" t="s">
-        <v>353</v>
+        <v>290</v>
       </c>
       <c r="B354" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C354" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D354" s="5">
         <v>0</v>
@@ -7238,13 +7238,13 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A355" s="1" t="s">
-        <v>354</v>
+        <v>291</v>
       </c>
       <c r="B355" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C355" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D355" s="5">
         <v>0</v>
@@ -7252,7 +7252,7 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A356" s="1" t="s">
-        <v>355</v>
+        <v>557</v>
       </c>
       <c r="B356" s="1">
         <v>3</v>
@@ -7266,7 +7266,7 @@
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A357" s="1" t="s">
-        <v>356</v>
+        <v>292</v>
       </c>
       <c r="B357" s="1">
         <v>3</v>
@@ -7280,13 +7280,13 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A358" s="1" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="B358" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C358" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D358" s="5">
         <v>0</v>
@@ -7294,13 +7294,13 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A359" s="1" t="s">
-        <v>358</v>
+        <v>294</v>
       </c>
       <c r="B359" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C359" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D359" s="5">
         <v>0</v>
@@ -7308,13 +7308,13 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A360" s="1" t="s">
-        <v>359</v>
+        <v>295</v>
       </c>
       <c r="B360" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C360" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D360" s="5">
         <v>0</v>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A361" s="1" t="s">
-        <v>360</v>
+        <v>296</v>
       </c>
       <c r="B361" s="1">
         <v>4</v>
@@ -7336,13 +7336,13 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A362" s="1" t="s">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="B362" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C362" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D362" s="5">
         <v>0</v>
@@ -7350,13 +7350,13 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A363" s="1" t="s">
-        <v>362</v>
+        <v>298</v>
       </c>
       <c r="B363" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C363" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D363" s="5">
         <v>0</v>
@@ -7364,7 +7364,7 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A364" s="1" t="s">
-        <v>363</v>
+        <v>299</v>
       </c>
       <c r="B364" s="1">
         <v>3</v>
@@ -7378,7 +7378,7 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A365" s="1" t="s">
-        <v>364</v>
+        <v>300</v>
       </c>
       <c r="B365" s="1">
         <v>3</v>
@@ -7392,7 +7392,7 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A366" s="1" t="s">
-        <v>365</v>
+        <v>301</v>
       </c>
       <c r="B366" s="1">
         <v>3</v>
@@ -7406,7 +7406,7 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A367" s="1" t="s">
-        <v>366</v>
+        <v>302</v>
       </c>
       <c r="B367" s="1">
         <v>3</v>
@@ -7420,7 +7420,7 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A368" s="1" t="s">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="B368" s="1">
         <v>3</v>
@@ -7434,7 +7434,7 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A369" s="1" t="s">
-        <v>368</v>
+        <v>304</v>
       </c>
       <c r="B369" s="1">
         <v>3</v>
@@ -7448,7 +7448,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A370" s="1" t="s">
-        <v>369</v>
+        <v>305</v>
       </c>
       <c r="B370" s="1">
         <v>3</v>
@@ -7462,7 +7462,7 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A371" s="1" t="s">
-        <v>370</v>
+        <v>306</v>
       </c>
       <c r="B371" s="1">
         <v>3</v>
@@ -7476,13 +7476,13 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A372" s="1" t="s">
-        <v>371</v>
+        <v>307</v>
       </c>
       <c r="B372" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C372" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D372" s="5">
         <v>0</v>
@@ -7490,7 +7490,7 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A373" s="1" t="s">
-        <v>372</v>
+        <v>308</v>
       </c>
       <c r="B373" s="1">
         <v>4</v>
@@ -7504,13 +7504,13 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A374" s="1" t="s">
-        <v>373</v>
+        <v>309</v>
       </c>
       <c r="B374" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C374" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D374" s="5">
         <v>0</v>
@@ -7518,13 +7518,13 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A375" s="1" t="s">
-        <v>374</v>
+        <v>310</v>
       </c>
       <c r="B375" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C375" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D375" s="5">
         <v>0</v>
@@ -7532,7 +7532,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A376" s="1" t="s">
-        <v>375</v>
+        <v>611</v>
       </c>
       <c r="B376" s="1">
         <v>3</v>
@@ -7546,13 +7546,13 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A377" s="1" t="s">
-        <v>376</v>
+        <v>613</v>
       </c>
       <c r="B377" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C377" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D377" s="5">
         <v>0</v>
@@ -7560,7 +7560,7 @@
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A378" s="1" t="s">
-        <v>377</v>
+        <v>612</v>
       </c>
       <c r="B378" s="1">
         <v>3</v>
@@ -7574,13 +7574,13 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A379" s="1" t="s">
-        <v>378</v>
+        <v>311</v>
       </c>
       <c r="B379" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C379" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D379" s="5">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A380" s="1" t="s">
-        <v>379</v>
+        <v>312</v>
       </c>
       <c r="B380" s="1">
         <v>3</v>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A381" s="1" t="s">
-        <v>380</v>
+        <v>313</v>
       </c>
       <c r="B381" s="1">
         <v>3</v>
@@ -7616,13 +7616,13 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A382" s="1" t="s">
-        <v>381</v>
+        <v>558</v>
       </c>
       <c r="B382" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C382" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D382" s="5">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A383" s="1" t="s">
-        <v>382</v>
+        <v>314</v>
       </c>
       <c r="B383" s="1">
         <v>3</v>
@@ -7644,13 +7644,13 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A384" s="1" t="s">
-        <v>383</v>
+        <v>315</v>
       </c>
       <c r="B384" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C384" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D384" s="5">
         <v>0</v>
@@ -7658,13 +7658,13 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A385" s="1" t="s">
-        <v>384</v>
+        <v>614</v>
       </c>
       <c r="B385" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C385" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D385" s="5">
         <v>0</v>
@@ -7672,13 +7672,13 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A386" s="1" t="s">
-        <v>385</v>
+        <v>316</v>
       </c>
       <c r="B386" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C386" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D386" s="5">
         <v>0</v>
@@ -7686,7 +7686,7 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A387" s="1" t="s">
-        <v>386</v>
+        <v>317</v>
       </c>
       <c r="B387" s="1">
         <v>2</v>
@@ -7700,13 +7700,13 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A388" s="1" t="s">
-        <v>387</v>
+        <v>318</v>
       </c>
       <c r="B388" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C388" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D388" s="5">
         <v>0</v>
@@ -7714,7 +7714,7 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A389" s="1" t="s">
-        <v>388</v>
+        <v>615</v>
       </c>
       <c r="B389" s="1">
         <v>2</v>
@@ -7728,7 +7728,7 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A390" s="1" t="s">
-        <v>389</v>
+        <v>319</v>
       </c>
       <c r="B390" s="1">
         <v>2</v>
@@ -7742,7 +7742,7 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A391" s="1" t="s">
-        <v>390</v>
+        <v>352</v>
       </c>
       <c r="B391" s="1">
         <v>2</v>
@@ -7756,7 +7756,7 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A392" s="1" t="s">
-        <v>391</v>
+        <v>320</v>
       </c>
       <c r="B392" s="1">
         <v>2</v>
@@ -7770,7 +7770,7 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A393" s="1" t="s">
-        <v>392</v>
+        <v>559</v>
       </c>
       <c r="B393" s="1">
         <v>2</v>
@@ -7784,7 +7784,7 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A394" s="1" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="B394" s="1">
         <v>2</v>
@@ -7798,7 +7798,7 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A395" s="1" t="s">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="B395" s="1">
         <v>2</v>
@@ -7812,13 +7812,13 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A396" s="1" t="s">
-        <v>395</v>
+        <v>323</v>
       </c>
       <c r="B396" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C396" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D396" s="5">
         <v>0</v>
@@ -7826,7 +7826,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A397" s="1" t="s">
-        <v>396</v>
+        <v>324</v>
       </c>
       <c r="B397" s="1">
         <v>2</v>
@@ -7840,13 +7840,13 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A398" s="1" t="s">
-        <v>397</v>
+        <v>325</v>
       </c>
       <c r="B398" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C398" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D398" s="5">
         <v>0</v>
@@ -7854,13 +7854,13 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A399" s="1" t="s">
-        <v>398</v>
+        <v>326</v>
       </c>
       <c r="B399" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C399" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D399" s="5">
         <v>0</v>
@@ -7868,7 +7868,7 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A400" s="1" t="s">
-        <v>399</v>
+        <v>560</v>
       </c>
       <c r="B400" s="1">
         <v>2</v>
@@ -7882,13 +7882,13 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A401" s="1" t="s">
-        <v>400</v>
+        <v>561</v>
       </c>
       <c r="B401" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C401" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D401" s="5">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A402" s="1" t="s">
-        <v>401</v>
+        <v>327</v>
       </c>
       <c r="B402" s="1">
         <v>2</v>
@@ -7910,7 +7910,7 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A403" s="1" t="s">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="B403" s="1">
         <v>2</v>
@@ -7924,7 +7924,7 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A404" s="1" t="s">
-        <v>403</v>
+        <v>562</v>
       </c>
       <c r="B404" s="1">
         <v>2</v>
@@ -7938,7 +7938,7 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A405" s="1" t="s">
-        <v>404</v>
+        <v>329</v>
       </c>
       <c r="B405" s="1">
         <v>2</v>
@@ -7952,7 +7952,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A406" s="1" t="s">
-        <v>405</v>
+        <v>616</v>
       </c>
       <c r="B406" s="1">
         <v>2</v>
@@ -7966,7 +7966,7 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A407" s="1" t="s">
-        <v>406</v>
+        <v>617</v>
       </c>
       <c r="B407" s="1">
         <v>2</v>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A408" s="1" t="s">
-        <v>407</v>
+        <v>330</v>
       </c>
       <c r="B408" s="1">
         <v>2</v>
@@ -7994,7 +7994,7 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A409" s="1" t="s">
-        <v>408</v>
+        <v>331</v>
       </c>
       <c r="B409" s="1">
         <v>2</v>
@@ -8008,7 +8008,7 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A410" s="1" t="s">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="B410" s="1">
         <v>2</v>
@@ -8022,7 +8022,7 @@
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A411" s="1" t="s">
-        <v>410</v>
+        <v>333</v>
       </c>
       <c r="B411" s="1">
         <v>2</v>
@@ -8036,7 +8036,7 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A412" s="1" t="s">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="B412" s="1">
         <v>2</v>
@@ -8050,7 +8050,7 @@
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A413" s="1" t="s">
-        <v>412</v>
+        <v>335</v>
       </c>
       <c r="B413" s="1">
         <v>2</v>
@@ -8064,7 +8064,7 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A414" s="1" t="s">
-        <v>413</v>
+        <v>563</v>
       </c>
       <c r="B414" s="1">
         <v>2</v>
@@ -8078,7 +8078,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A415" s="1" t="s">
-        <v>414</v>
+        <v>336</v>
       </c>
       <c r="B415" s="1">
         <v>2</v>
@@ -8092,7 +8092,7 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A416" s="1" t="s">
-        <v>415</v>
+        <v>337</v>
       </c>
       <c r="B416" s="1">
         <v>2</v>
@@ -8106,7 +8106,7 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A417" s="1" t="s">
-        <v>416</v>
+        <v>338</v>
       </c>
       <c r="B417" s="1">
         <v>2</v>
@@ -8120,13 +8120,13 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A418" s="1" t="s">
-        <v>417</v>
+        <v>339</v>
       </c>
       <c r="B418" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C418" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D418" s="5">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A419" s="1" t="s">
-        <v>418</v>
+        <v>340</v>
       </c>
       <c r="B419" s="1">
         <v>2</v>
@@ -8148,13 +8148,13 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A420" s="1" t="s">
-        <v>419</v>
+        <v>564</v>
       </c>
       <c r="B420" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C420" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D420" s="5">
         <v>0</v>
@@ -8162,13 +8162,13 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A421" s="1" t="s">
-        <v>420</v>
+        <v>618</v>
       </c>
       <c r="B421" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C421" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D421" s="5">
         <v>0</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A422" s="1" t="s">
-        <v>421</v>
+        <v>341</v>
       </c>
       <c r="B422" s="1">
         <v>2</v>
@@ -8190,13 +8190,13 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A423" s="1" t="s">
-        <v>422</v>
+        <v>565</v>
       </c>
       <c r="B423" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C423" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D423" s="5">
         <v>0</v>
@@ -8204,7 +8204,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A424" s="1" t="s">
-        <v>423</v>
+        <v>342</v>
       </c>
       <c r="B424" s="1">
         <v>2</v>
@@ -8218,13 +8218,13 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A425" s="1" t="s">
-        <v>424</v>
+        <v>619</v>
       </c>
       <c r="B425" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C425" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D425" s="5">
         <v>0</v>
@@ -8232,7 +8232,7 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A426" s="1" t="s">
-        <v>425</v>
+        <v>566</v>
       </c>
       <c r="B426" s="1">
         <v>2</v>
@@ -8246,7 +8246,7 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A427" s="1" t="s">
-        <v>426</v>
+        <v>343</v>
       </c>
       <c r="B427" s="1">
         <v>2</v>
@@ -8260,7 +8260,7 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A428" s="1" t="s">
-        <v>427</v>
+        <v>344</v>
       </c>
       <c r="B428" s="1">
         <v>2</v>
@@ -8274,7 +8274,7 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A429" s="1" t="s">
-        <v>428</v>
+        <v>345</v>
       </c>
       <c r="B429" s="1">
         <v>2</v>
@@ -8288,7 +8288,7 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A430" s="1" t="s">
-        <v>429</v>
+        <v>346</v>
       </c>
       <c r="B430" s="1">
         <v>2</v>
@@ -8302,7 +8302,7 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A431" s="1" t="s">
-        <v>430</v>
+        <v>347</v>
       </c>
       <c r="B431" s="1">
         <v>2</v>
@@ -8316,7 +8316,7 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A432" s="1" t="s">
-        <v>431</v>
+        <v>348</v>
       </c>
       <c r="B432" s="1">
         <v>2</v>
@@ -8330,7 +8330,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A433" s="1" t="s">
-        <v>432</v>
+        <v>349</v>
       </c>
       <c r="B433" s="1">
         <v>2</v>
@@ -8344,7 +8344,7 @@
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A434" s="1" t="s">
-        <v>433</v>
+        <v>350</v>
       </c>
       <c r="B434" s="1">
         <v>2</v>
@@ -8358,7 +8358,7 @@
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A435" s="1" t="s">
-        <v>434</v>
+        <v>351</v>
       </c>
       <c r="B435" s="1">
         <v>2</v>
@@ -8372,7 +8372,7 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A436" s="1" t="s">
-        <v>435</v>
+        <v>620</v>
       </c>
       <c r="B436" s="1">
         <v>2</v>
@@ -8386,7 +8386,7 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A437" s="1" t="s">
-        <v>436</v>
+        <v>352</v>
       </c>
       <c r="B437" s="1">
         <v>2</v>
@@ -8400,7 +8400,7 @@
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A438" s="1" t="s">
-        <v>437</v>
+        <v>353</v>
       </c>
       <c r="B438" s="1">
         <v>2</v>
@@ -8414,13 +8414,13 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A439" s="1" t="s">
-        <v>438</v>
+        <v>354</v>
       </c>
       <c r="B439" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C439" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D439" s="5">
         <v>0</v>
@@ -8428,7 +8428,7 @@
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A440" s="1" t="s">
-        <v>439</v>
+        <v>355</v>
       </c>
       <c r="B440" s="1">
         <v>2</v>
@@ -8442,13 +8442,13 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A441" s="1" t="s">
-        <v>440</v>
+        <v>356</v>
       </c>
       <c r="B441" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C441" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D441" s="5">
         <v>0</v>
@@ -8456,7 +8456,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A442" s="1" t="s">
-        <v>441</v>
+        <v>567</v>
       </c>
       <c r="B442" s="1">
         <v>2</v>
@@ -8470,7 +8470,7 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A443" s="1" t="s">
-        <v>442</v>
+        <v>357</v>
       </c>
       <c r="B443" s="1">
         <v>2</v>
@@ -8484,7 +8484,7 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A444" s="1" t="s">
-        <v>443</v>
+        <v>358</v>
       </c>
       <c r="B444" s="1">
         <v>2</v>
@@ -8498,13 +8498,13 @@
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A445" s="1" t="s">
-        <v>444</v>
+        <v>359</v>
       </c>
       <c r="B445" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C445" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D445" s="5">
         <v>0</v>
@@ -8512,7 +8512,7 @@
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A446" s="1" t="s">
-        <v>445</v>
+        <v>360</v>
       </c>
       <c r="B446" s="1">
         <v>2</v>
@@ -8526,13 +8526,13 @@
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A447" s="1" t="s">
-        <v>446</v>
+        <v>361</v>
       </c>
       <c r="B447" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C447" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D447" s="5">
         <v>0</v>
@@ -8540,13 +8540,13 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A448" s="1" t="s">
-        <v>447</v>
+        <v>362</v>
       </c>
       <c r="B448" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C448" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D448" s="5">
         <v>0</v>
@@ -8554,7 +8554,7 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A449" s="1" t="s">
-        <v>448</v>
+        <v>363</v>
       </c>
       <c r="B449" s="1">
         <v>2</v>
@@ -8568,13 +8568,13 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A450" s="1" t="s">
-        <v>449</v>
+        <v>364</v>
       </c>
       <c r="B450" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C450" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D450" s="5">
         <v>0</v>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A451" s="1" t="s">
-        <v>450</v>
+        <v>568</v>
       </c>
       <c r="B451" s="1">
         <v>2</v>
@@ -8596,7 +8596,7 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A452" s="1" t="s">
-        <v>451</v>
+        <v>365</v>
       </c>
       <c r="B452" s="1">
         <v>2</v>
@@ -8610,7 +8610,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A453" s="1" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
       <c r="B453" s="1">
         <v>2</v>
@@ -8624,7 +8624,7 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A454" s="1" t="s">
-        <v>453</v>
+        <v>367</v>
       </c>
       <c r="B454" s="1">
         <v>2</v>
@@ -8638,13 +8638,13 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A455" s="1" t="s">
-        <v>454</v>
+        <v>368</v>
       </c>
       <c r="B455" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C455" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D455" s="5">
         <v>0</v>
@@ -8652,7 +8652,7 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A456" s="1" t="s">
-        <v>455</v>
+        <v>369</v>
       </c>
       <c r="B456" s="1">
         <v>2</v>
@@ -8666,13 +8666,13 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A457" s="1" t="s">
-        <v>456</v>
+        <v>370</v>
       </c>
       <c r="B457" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C457" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D457" s="5">
         <v>0</v>
@@ -8680,7 +8680,7 @@
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A458" s="1" t="s">
-        <v>457</v>
+        <v>371</v>
       </c>
       <c r="B458" s="1">
         <v>2</v>
@@ -8694,7 +8694,7 @@
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A459" s="1" t="s">
-        <v>458</v>
+        <v>372</v>
       </c>
       <c r="B459" s="1">
         <v>2</v>
@@ -8708,13 +8708,13 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A460" s="1" t="s">
-        <v>459</v>
+        <v>373</v>
       </c>
       <c r="B460" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C460" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D460" s="5">
         <v>0</v>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A461" s="1" t="s">
-        <v>460</v>
+        <v>374</v>
       </c>
       <c r="B461" s="1">
         <v>2</v>
@@ -8736,13 +8736,13 @@
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A462" s="1" t="s">
-        <v>461</v>
+        <v>375</v>
       </c>
       <c r="B462" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C462" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D462" s="5">
         <v>0</v>
@@ -8750,13 +8750,13 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A463" s="1" t="s">
-        <v>462</v>
+        <v>376</v>
       </c>
       <c r="B463" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C463" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D463" s="5">
         <v>0</v>
@@ -8764,7 +8764,7 @@
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A464" s="1" t="s">
-        <v>463</v>
+        <v>377</v>
       </c>
       <c r="B464" s="1">
         <v>2</v>
@@ -8778,13 +8778,13 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A465" s="1" t="s">
-        <v>464</v>
+        <v>378</v>
       </c>
       <c r="B465" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C465" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D465" s="5">
         <v>0</v>
@@ -8792,13 +8792,13 @@
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A466" s="1" t="s">
-        <v>465</v>
+        <v>569</v>
       </c>
       <c r="B466" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C466" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D466" s="5">
         <v>0</v>
@@ -8806,7 +8806,7 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A467" s="1" t="s">
-        <v>466</v>
+        <v>379</v>
       </c>
       <c r="B467" s="1">
         <v>2</v>
@@ -8820,7 +8820,7 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A468" s="1" t="s">
-        <v>467</v>
+        <v>380</v>
       </c>
       <c r="B468" s="1">
         <v>1</v>
@@ -8834,13 +8834,13 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A469" s="1" t="s">
-        <v>468</v>
+        <v>530</v>
       </c>
       <c r="B469" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C469" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D469" s="5">
         <v>0</v>
@@ -8848,7 +8848,7 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A470" s="1" t="s">
-        <v>469</v>
+        <v>381</v>
       </c>
       <c r="B470" s="1">
         <v>1</v>
@@ -8862,7 +8862,7 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A471" s="1" t="s">
-        <v>470</v>
+        <v>382</v>
       </c>
       <c r="B471" s="1">
         <v>1</v>
@@ -8876,7 +8876,7 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A472" s="1" t="s">
-        <v>471</v>
+        <v>383</v>
       </c>
       <c r="B472" s="1">
         <v>1</v>
@@ -8890,7 +8890,7 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A473" s="1" t="s">
-        <v>472</v>
+        <v>384</v>
       </c>
       <c r="B473" s="1">
         <v>1</v>
@@ -8904,7 +8904,7 @@
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A474" s="1" t="s">
-        <v>473</v>
+        <v>385</v>
       </c>
       <c r="B474" s="1">
         <v>1</v>
@@ -8918,7 +8918,7 @@
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A475" s="1" t="s">
-        <v>474</v>
+        <v>386</v>
       </c>
       <c r="B475" s="1">
         <v>1</v>
@@ -8932,7 +8932,7 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A476" s="1" t="s">
-        <v>475</v>
+        <v>387</v>
       </c>
       <c r="B476" s="1">
         <v>1</v>
@@ -8946,7 +8946,7 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A477" s="1" t="s">
-        <v>476</v>
+        <v>388</v>
       </c>
       <c r="B477" s="1">
         <v>1</v>
@@ -8960,7 +8960,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A478" s="1" t="s">
-        <v>477</v>
+        <v>389</v>
       </c>
       <c r="B478" s="1">
         <v>1</v>
@@ -8974,7 +8974,7 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A479" s="1" t="s">
-        <v>478</v>
+        <v>390</v>
       </c>
       <c r="B479" s="1">
         <v>1</v>
@@ -8988,7 +8988,7 @@
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A480" s="1" t="s">
-        <v>479</v>
+        <v>391</v>
       </c>
       <c r="B480" s="1">
         <v>1</v>
@@ -9002,13 +9002,13 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A481" s="1" t="s">
-        <v>480</v>
+        <v>392</v>
       </c>
       <c r="B481" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C481" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D481" s="5">
         <v>0</v>
@@ -9016,7 +9016,7 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A482" s="1" t="s">
-        <v>481</v>
+        <v>570</v>
       </c>
       <c r="B482" s="1">
         <v>1</v>
@@ -9030,13 +9030,13 @@
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A483" s="1" t="s">
-        <v>482</v>
+        <v>393</v>
       </c>
       <c r="B483" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C483" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D483" s="5">
         <v>0</v>
@@ -9044,13 +9044,13 @@
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A484" s="1" t="s">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="B484" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C484" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D484" s="5">
         <v>0</v>
@@ -9058,7 +9058,7 @@
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A485" s="1" t="s">
-        <v>484</v>
+        <v>395</v>
       </c>
       <c r="B485" s="1">
         <v>1</v>
@@ -9072,13 +9072,13 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A486" s="1" t="s">
-        <v>485</v>
+        <v>396</v>
       </c>
       <c r="B486" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C486" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D486" s="5">
         <v>0</v>
@@ -9086,7 +9086,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A487" s="1" t="s">
-        <v>486</v>
+        <v>571</v>
       </c>
       <c r="B487" s="1">
         <v>1</v>
@@ -9100,7 +9100,7 @@
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A488" s="1" t="s">
-        <v>487</v>
+        <v>397</v>
       </c>
       <c r="B488" s="1">
         <v>1</v>
@@ -9114,13 +9114,13 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A489" s="1" t="s">
-        <v>488</v>
+        <v>572</v>
       </c>
       <c r="B489" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C489" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D489" s="5">
         <v>0</v>
@@ -9128,7 +9128,7 @@
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A490" s="1" t="s">
-        <v>489</v>
+        <v>398</v>
       </c>
       <c r="B490" s="1">
         <v>1</v>
@@ -9142,13 +9142,13 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A491" s="1" t="s">
-        <v>490</v>
+        <v>399</v>
       </c>
       <c r="B491" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C491" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D491" s="5">
         <v>0</v>
@@ -9156,7 +9156,7 @@
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A492" s="1" t="s">
-        <v>491</v>
+        <v>400</v>
       </c>
       <c r="B492" s="1">
         <v>1</v>
@@ -9170,7 +9170,7 @@
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A493" s="1" t="s">
-        <v>492</v>
+        <v>401</v>
       </c>
       <c r="B493" s="1">
         <v>1</v>
@@ -9184,7 +9184,7 @@
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A494" s="1" t="s">
-        <v>493</v>
+        <v>573</v>
       </c>
       <c r="B494" s="1">
         <v>1</v>
@@ -9198,7 +9198,7 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A495" s="1" t="s">
-        <v>494</v>
+        <v>574</v>
       </c>
       <c r="B495" s="1">
         <v>1</v>
@@ -9212,7 +9212,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A496" s="1" t="s">
-        <v>495</v>
+        <v>402</v>
       </c>
       <c r="B496" s="1">
         <v>1</v>
@@ -9226,7 +9226,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A497" s="1" t="s">
-        <v>496</v>
+        <v>575</v>
       </c>
       <c r="B497" s="1">
         <v>1</v>
@@ -9240,7 +9240,7 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A498" s="1" t="s">
-        <v>497</v>
+        <v>403</v>
       </c>
       <c r="B498" s="1">
         <v>1</v>
@@ -9254,13 +9254,13 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A499" s="1" t="s">
-        <v>498</v>
+        <v>404</v>
       </c>
       <c r="B499" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C499" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D499" s="5">
         <v>0</v>
@@ -9268,7 +9268,7 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A500" s="1" t="s">
-        <v>499</v>
+        <v>405</v>
       </c>
       <c r="B500" s="1">
         <v>1</v>
@@ -9282,13 +9282,13 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A501" s="1" t="s">
-        <v>500</v>
+        <v>406</v>
       </c>
       <c r="B501" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C501" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D501" s="5">
         <v>0</v>
@@ -9296,13 +9296,13 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A502" s="1" t="s">
-        <v>501</v>
+        <v>407</v>
       </c>
       <c r="B502" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C502" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D502" s="5">
         <v>0</v>
@@ -9310,7 +9310,7 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A503" s="1" t="s">
-        <v>502</v>
+        <v>408</v>
       </c>
       <c r="B503" s="1">
         <v>1</v>
@@ -9324,13 +9324,13 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A504" s="1" t="s">
-        <v>503</v>
+        <v>409</v>
       </c>
       <c r="B504" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C504" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D504" s="5">
         <v>0</v>
@@ -9338,7 +9338,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A505" s="1" t="s">
-        <v>504</v>
+        <v>410</v>
       </c>
       <c r="B505" s="1">
         <v>1</v>
@@ -9352,7 +9352,7 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A506" s="1" t="s">
-        <v>505</v>
+        <v>411</v>
       </c>
       <c r="B506" s="1">
         <v>1</v>
@@ -9366,7 +9366,7 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A507" s="1" t="s">
-        <v>506</v>
+        <v>412</v>
       </c>
       <c r="B507" s="1">
         <v>1</v>
@@ -9380,7 +9380,7 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A508" s="1" t="s">
-        <v>507</v>
+        <v>413</v>
       </c>
       <c r="B508" s="1">
         <v>1</v>
@@ -9394,7 +9394,7 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A509" s="1" t="s">
-        <v>508</v>
+        <v>414</v>
       </c>
       <c r="B509" s="1">
         <v>1</v>
@@ -9408,7 +9408,7 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A510" s="1" t="s">
-        <v>509</v>
+        <v>415</v>
       </c>
       <c r="B510" s="1">
         <v>1</v>
@@ -9422,7 +9422,7 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A511" s="1" t="s">
-        <v>510</v>
+        <v>416</v>
       </c>
       <c r="B511" s="1">
         <v>1</v>
@@ -9436,7 +9436,7 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A512" s="1" t="s">
-        <v>511</v>
+        <v>621</v>
       </c>
       <c r="B512" s="1">
         <v>1</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A513" s="1" t="s">
-        <v>512</v>
+        <v>417</v>
       </c>
       <c r="B513" s="1">
         <v>1</v>
@@ -9464,7 +9464,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A514" s="1" t="s">
-        <v>513</v>
+        <v>418</v>
       </c>
       <c r="B514" s="1">
         <v>1</v>
@@ -9478,7 +9478,7 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A515" s="1" t="s">
-        <v>514</v>
+        <v>576</v>
       </c>
       <c r="B515" s="1">
         <v>1</v>
@@ -9492,7 +9492,7 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A516" s="1" t="s">
-        <v>515</v>
+        <v>419</v>
       </c>
       <c r="B516" s="1">
         <v>1</v>
@@ -9506,13 +9506,13 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A517" s="1" t="s">
-        <v>516</v>
+        <v>420</v>
       </c>
       <c r="B517" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C517" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D517" s="5">
         <v>0</v>
@@ -9520,7 +9520,7 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A518" s="1" t="s">
-        <v>517</v>
+        <v>421</v>
       </c>
       <c r="B518" s="1">
         <v>1</v>
@@ -9534,13 +9534,13 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A519" s="1" t="s">
-        <v>518</v>
+        <v>422</v>
       </c>
       <c r="B519" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C519" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D519" s="5">
         <v>0</v>
@@ -9548,7 +9548,7 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A520" s="1" t="s">
-        <v>519</v>
+        <v>423</v>
       </c>
       <c r="B520" s="1">
         <v>1</v>
@@ -9562,7 +9562,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A521" s="1" t="s">
-        <v>520</v>
+        <v>424</v>
       </c>
       <c r="B521" s="1">
         <v>1</v>
@@ -9576,7 +9576,7 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A522" s="1" t="s">
-        <v>521</v>
+        <v>425</v>
       </c>
       <c r="B522" s="1">
         <v>1</v>
@@ -9590,7 +9590,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A523" s="1" t="s">
-        <v>522</v>
+        <v>426</v>
       </c>
       <c r="B523" s="1">
         <v>1</v>
@@ -9604,13 +9604,13 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A524" s="1" t="s">
-        <v>523</v>
+        <v>427</v>
       </c>
       <c r="B524" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C524" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D524" s="5">
         <v>0</v>
@@ -9618,7 +9618,7 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A525" s="1" t="s">
-        <v>524</v>
+        <v>428</v>
       </c>
       <c r="B525" s="1">
         <v>1</v>
@@ -9632,13 +9632,13 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A526" s="1" t="s">
-        <v>525</v>
+        <v>429</v>
       </c>
       <c r="B526" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C526" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D526" s="5">
         <v>0</v>
@@ -9646,7 +9646,7 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A527" s="1" t="s">
-        <v>526</v>
+        <v>430</v>
       </c>
       <c r="B527" s="1">
         <v>1</v>
@@ -9660,7 +9660,7 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A528" s="1" t="s">
-        <v>527</v>
+        <v>431</v>
       </c>
       <c r="B528" s="1">
         <v>1</v>
@@ -9674,7 +9674,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A529" s="1" t="s">
-        <v>528</v>
+        <v>432</v>
       </c>
       <c r="B529" s="1">
         <v>1</v>
@@ -9688,7 +9688,7 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A530" s="1" t="s">
-        <v>529</v>
+        <v>433</v>
       </c>
       <c r="B530" s="1">
         <v>1</v>
@@ -9702,7 +9702,7 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A531" s="1" t="s">
-        <v>530</v>
+        <v>434</v>
       </c>
       <c r="B531" s="1">
         <v>1</v>
@@ -9716,7 +9716,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A532" s="1" t="s">
-        <v>531</v>
+        <v>435</v>
       </c>
       <c r="B532" s="1">
         <v>1</v>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A533" s="1" t="s">
-        <v>532</v>
+        <v>436</v>
       </c>
       <c r="B533" s="1">
         <v>1</v>
@@ -9744,7 +9744,7 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A534" s="1" t="s">
-        <v>533</v>
+        <v>437</v>
       </c>
       <c r="B534" s="1">
         <v>1</v>
@@ -9758,7 +9758,7 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A535" s="1" t="s">
-        <v>534</v>
+        <v>438</v>
       </c>
       <c r="B535" s="1">
         <v>1</v>
@@ -9772,7 +9772,7 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A536" s="1" t="s">
-        <v>535</v>
+        <v>439</v>
       </c>
       <c r="B536" s="1">
         <v>1</v>
@@ -9786,7 +9786,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A537" s="1" t="s">
-        <v>536</v>
+        <v>440</v>
       </c>
       <c r="B537" s="1">
         <v>1</v>
@@ -9800,7 +9800,7 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A538" s="1" t="s">
-        <v>537</v>
+        <v>441</v>
       </c>
       <c r="B538" s="1">
         <v>1</v>
@@ -9814,13 +9814,13 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A539" s="1" t="s">
-        <v>538</v>
+        <v>442</v>
       </c>
       <c r="B539" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C539" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D539" s="5">
         <v>0</v>
@@ -9828,7 +9828,7 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A540" s="1" t="s">
-        <v>539</v>
+        <v>443</v>
       </c>
       <c r="B540" s="1">
         <v>1</v>
@@ -9842,7 +9842,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A541" s="1" t="s">
-        <v>540</v>
+        <v>444</v>
       </c>
       <c r="B541" s="1">
         <v>2</v>
@@ -9856,13 +9856,13 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A542" s="1" t="s">
-        <v>541</v>
+        <v>445</v>
       </c>
       <c r="B542" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C542" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D542" s="5">
         <v>0</v>
@@ -9870,13 +9870,13 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A543" s="1" t="s">
-        <v>542</v>
+        <v>446</v>
       </c>
       <c r="B543" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C543" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D543" s="5">
         <v>0</v>
@@ -9884,7 +9884,7 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A544" s="1" t="s">
-        <v>543</v>
+        <v>447</v>
       </c>
       <c r="B544" s="1">
         <v>2</v>
@@ -9898,7 +9898,7 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A545" s="1" t="s">
-        <v>544</v>
+        <v>448</v>
       </c>
       <c r="B545" s="1">
         <v>1</v>
@@ -9912,13 +9912,13 @@
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A546" s="1" t="s">
-        <v>545</v>
+        <v>449</v>
       </c>
       <c r="B546" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C546" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D546" s="5">
         <v>0</v>
@@ -9926,7 +9926,7 @@
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A547" s="1" t="s">
-        <v>546</v>
+        <v>450</v>
       </c>
       <c r="B547" s="1">
         <v>1</v>
@@ -9940,7 +9940,7 @@
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A548" s="1" t="s">
-        <v>547</v>
+        <v>451</v>
       </c>
       <c r="B548" s="1">
         <v>1</v>
@@ -9954,7 +9954,7 @@
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A549" s="1" t="s">
-        <v>548</v>
+        <v>452</v>
       </c>
       <c r="B549" s="1">
         <v>1</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A550" s="1" t="s">
-        <v>549</v>
+        <v>622</v>
       </c>
       <c r="B550" s="1">
         <v>1</v>
@@ -9982,7 +9982,7 @@
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A551" s="1" t="s">
-        <v>550</v>
+        <v>453</v>
       </c>
       <c r="B551" s="1">
         <v>1</v>
@@ -9996,13 +9996,13 @@
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A552" s="1" t="s">
-        <v>551</v>
+        <v>454</v>
       </c>
       <c r="B552" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C552" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D552" s="5">
         <v>0</v>
@@ -10010,7 +10010,7 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A553" s="1" t="s">
-        <v>552</v>
+        <v>455</v>
       </c>
       <c r="B553" s="1">
         <v>1</v>
@@ -10024,13 +10024,13 @@
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A554" s="1" t="s">
-        <v>553</v>
+        <v>456</v>
       </c>
       <c r="B554" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C554" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D554" s="5">
         <v>0</v>
@@ -10038,7 +10038,7 @@
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A555" s="1" t="s">
-        <v>554</v>
+        <v>457</v>
       </c>
       <c r="B555" s="1">
         <v>1</v>
@@ -10052,7 +10052,7 @@
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A556" s="1" t="s">
-        <v>555</v>
+        <v>623</v>
       </c>
       <c r="B556" s="1">
         <v>1</v>
@@ -10066,7 +10066,7 @@
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A557" s="1" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="B557" s="1">
         <v>1</v>
@@ -10080,7 +10080,7 @@
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A558" s="1" t="s">
-        <v>557</v>
+        <v>624</v>
       </c>
       <c r="B558" s="1">
         <v>1</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A559" s="1" t="s">
-        <v>558</v>
+        <v>458</v>
       </c>
       <c r="B559" s="1">
         <v>1</v>
@@ -10108,13 +10108,13 @@
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A560" s="1" t="s">
-        <v>559</v>
+        <v>459</v>
       </c>
       <c r="B560" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C560" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D560" s="5">
         <v>0</v>
@@ -10122,7 +10122,7 @@
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A561" s="1" t="s">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="B561" s="1">
         <v>1</v>
@@ -10136,13 +10136,13 @@
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A562" s="1" t="s">
-        <v>561</v>
+        <v>461</v>
       </c>
       <c r="B562" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C562" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D562" s="5">
         <v>0</v>
@@ -10150,7 +10150,7 @@
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A563" s="1" t="s">
-        <v>562</v>
+        <v>462</v>
       </c>
       <c r="B563" s="1">
         <v>1</v>
@@ -10164,13 +10164,13 @@
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A564" s="1" t="s">
-        <v>563</v>
+        <v>463</v>
       </c>
       <c r="B564" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C564" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D564" s="5">
         <v>0</v>
@@ -10178,7 +10178,7 @@
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A565" s="1" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="B565" s="1">
         <v>1</v>
@@ -10192,7 +10192,7 @@
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A566" s="1" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="B566" s="1">
         <v>1</v>
@@ -10206,7 +10206,7 @@
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A567" s="1" t="s">
-        <v>566</v>
+        <v>464</v>
       </c>
       <c r="B567" s="1">
         <v>1</v>
@@ -10220,7 +10220,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A568" s="1" t="s">
-        <v>567</v>
+        <v>465</v>
       </c>
       <c r="B568" s="1">
         <v>1</v>
@@ -10234,7 +10234,7 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A569" s="1" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="B569" s="1">
         <v>1</v>
@@ -10248,7 +10248,7 @@
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A570" s="1" t="s">
-        <v>569</v>
+        <v>466</v>
       </c>
       <c r="B570" s="1">
         <v>1</v>
@@ -10262,7 +10262,7 @@
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A571" s="1" t="s">
-        <v>570</v>
+        <v>467</v>
       </c>
       <c r="B571" s="1">
         <v>1</v>
@@ -10276,7 +10276,7 @@
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A572" s="1" t="s">
-        <v>571</v>
+        <v>468</v>
       </c>
       <c r="B572" s="1">
         <v>1</v>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A573" s="1" t="s">
-        <v>572</v>
+        <v>469</v>
       </c>
       <c r="B573" s="1">
         <v>1</v>
@@ -10304,7 +10304,7 @@
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A574" s="1" t="s">
-        <v>573</v>
+        <v>470</v>
       </c>
       <c r="B574" s="1">
         <v>1</v>
@@ -10318,7 +10318,7 @@
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A575" s="1" t="s">
-        <v>574</v>
+        <v>471</v>
       </c>
       <c r="B575" s="1">
         <v>1</v>
@@ -10332,7 +10332,7 @@
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A576" s="1" t="s">
-        <v>575</v>
+        <v>472</v>
       </c>
       <c r="B576" s="1">
         <v>1</v>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A577" s="1" t="s">
-        <v>576</v>
+        <v>473</v>
       </c>
       <c r="B577" s="1">
         <v>1</v>
@@ -10360,7 +10360,7 @@
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A578" s="1" t="s">
-        <v>577</v>
+        <v>474</v>
       </c>
       <c r="B578" s="1">
         <v>1</v>
@@ -10374,7 +10374,7 @@
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A579" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B579" s="1">
         <v>1</v>
@@ -10388,13 +10388,13 @@
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A580" s="1" t="s">
-        <v>579</v>
+        <v>475</v>
       </c>
       <c r="B580" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C580" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D580" s="5">
         <v>0</v>
@@ -10402,7 +10402,7 @@
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A581" s="1" t="s">
-        <v>580</v>
+        <v>476</v>
       </c>
       <c r="B581" s="1">
         <v>1</v>
@@ -10416,13 +10416,13 @@
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A582" s="1" t="s">
-        <v>581</v>
+        <v>477</v>
       </c>
       <c r="B582" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C582" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D582" s="5">
         <v>0</v>
@@ -10430,7 +10430,7 @@
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A583" s="1" t="s">
-        <v>582</v>
+        <v>478</v>
       </c>
       <c r="B583" s="1">
         <v>1</v>
@@ -10458,7 +10458,7 @@
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A585" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B585" s="1">
         <v>1</v>
@@ -10472,7 +10472,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A586" s="1" t="s">
-        <v>585</v>
+        <v>625</v>
       </c>
       <c r="B586" s="1">
         <v>1</v>
@@ -10486,7 +10486,7 @@
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A587" s="1" t="s">
-        <v>586</v>
+        <v>626</v>
       </c>
       <c r="B587" s="1">
         <v>1</v>
@@ -10500,7 +10500,7 @@
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A588" s="1" t="s">
-        <v>587</v>
+        <v>479</v>
       </c>
       <c r="B588" s="1">
         <v>1</v>
@@ -10514,7 +10514,7 @@
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A589" s="1" t="s">
-        <v>588</v>
+        <v>628</v>
       </c>
       <c r="B589" s="1">
         <v>1</v>
@@ -10528,7 +10528,7 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A590" s="1" t="s">
-        <v>589</v>
+        <v>627</v>
       </c>
       <c r="B590" s="1">
         <v>1</v>
@@ -10542,7 +10542,7 @@
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A591" s="1" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B591" s="1">
         <v>1</v>
@@ -10556,7 +10556,7 @@
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A592" s="1" t="s">
-        <v>591</v>
+        <v>480</v>
       </c>
       <c r="B592" s="1">
         <v>1</v>
@@ -10570,7 +10570,7 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A593" s="1" t="s">
-        <v>592</v>
+        <v>481</v>
       </c>
       <c r="B593" s="1">
         <v>1</v>
@@ -10584,7 +10584,7 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A594" s="1" t="s">
-        <v>593</v>
+        <v>482</v>
       </c>
       <c r="B594" s="1">
         <v>1</v>
@@ -10598,7 +10598,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A595" s="1" t="s">
-        <v>594</v>
+        <v>483</v>
       </c>
       <c r="B595" s="1">
         <v>1</v>
@@ -10612,7 +10612,7 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A596" s="1" t="s">
-        <v>595</v>
+        <v>484</v>
       </c>
       <c r="B596" s="1">
         <v>1</v>
@@ -10626,7 +10626,7 @@
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A597" s="1" t="s">
-        <v>596</v>
+        <v>485</v>
       </c>
       <c r="B597" s="1">
         <v>1</v>
@@ -10640,7 +10640,7 @@
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A598" s="1" t="s">
-        <v>597</v>
+        <v>486</v>
       </c>
       <c r="B598" s="1">
         <v>1</v>
@@ -10654,7 +10654,7 @@
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A599" s="1" t="s">
-        <v>598</v>
+        <v>487</v>
       </c>
       <c r="B599" s="1">
         <v>1</v>
@@ -10668,7 +10668,7 @@
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A600" s="1" t="s">
-        <v>599</v>
+        <v>488</v>
       </c>
       <c r="B600" s="1">
         <v>1</v>
@@ -10682,7 +10682,7 @@
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A601" s="1" t="s">
-        <v>600</v>
+        <v>489</v>
       </c>
       <c r="B601" s="1">
         <v>1</v>
@@ -10696,7 +10696,7 @@
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A602" s="1" t="s">
-        <v>601</v>
+        <v>490</v>
       </c>
       <c r="B602" s="1">
         <v>1</v>
@@ -10710,7 +10710,7 @@
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A603" s="1" t="s">
-        <v>602</v>
+        <v>491</v>
       </c>
       <c r="B603" s="1">
         <v>1</v>
@@ -10724,7 +10724,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A604" s="1" t="s">
-        <v>603</v>
+        <v>492</v>
       </c>
       <c r="B604" s="1">
         <v>1</v>
@@ -10738,7 +10738,7 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A605" s="1" t="s">
-        <v>604</v>
+        <v>493</v>
       </c>
       <c r="B605" s="1">
         <v>1</v>
@@ -10752,7 +10752,7 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A606" s="1" t="s">
-        <v>605</v>
+        <v>494</v>
       </c>
       <c r="B606" s="1">
         <v>1</v>
@@ -10766,7 +10766,7 @@
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A607" s="1" t="s">
-        <v>606</v>
+        <v>495</v>
       </c>
       <c r="B607" s="1">
         <v>1</v>
@@ -10780,7 +10780,7 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A608" s="1" t="s">
-        <v>607</v>
+        <v>496</v>
       </c>
       <c r="B608" s="1">
         <v>1</v>
@@ -10794,7 +10794,7 @@
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A609" s="1" t="s">
-        <v>608</v>
+        <v>497</v>
       </c>
       <c r="B609" s="1">
         <v>1</v>
@@ -10808,7 +10808,7 @@
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A610" s="1" t="s">
-        <v>609</v>
+        <v>498</v>
       </c>
       <c r="B610" s="1">
         <v>1</v>
@@ -10822,7 +10822,7 @@
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A611" s="1" t="s">
-        <v>610</v>
+        <v>499</v>
       </c>
       <c r="B611" s="1">
         <v>1</v>
@@ -10836,7 +10836,7 @@
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A612" s="1" t="s">
-        <v>611</v>
+        <v>500</v>
       </c>
       <c r="B612" s="1">
         <v>1</v>
@@ -10850,7 +10850,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A613" s="1" t="s">
-        <v>612</v>
+        <v>501</v>
       </c>
       <c r="B613" s="1">
         <v>1</v>
@@ -10864,7 +10864,7 @@
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A614" s="1" t="s">
-        <v>613</v>
+        <v>502</v>
       </c>
       <c r="B614" s="1">
         <v>1</v>
@@ -10878,7 +10878,7 @@
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A615" s="1" t="s">
-        <v>614</v>
+        <v>503</v>
       </c>
       <c r="B615" s="1">
         <v>1</v>
@@ -10892,7 +10892,7 @@
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A616" s="1" t="s">
-        <v>615</v>
+        <v>504</v>
       </c>
       <c r="B616" s="1">
         <v>1</v>
@@ -10906,7 +10906,7 @@
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A617" s="1" t="s">
-        <v>616</v>
+        <v>505</v>
       </c>
       <c r="B617" s="1">
         <v>1</v>
@@ -10920,7 +10920,7 @@
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A618" s="1" t="s">
-        <v>617</v>
+        <v>585</v>
       </c>
       <c r="B618" s="1">
         <v>1</v>
@@ -10934,7 +10934,7 @@
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A619" s="1" t="s">
-        <v>618</v>
+        <v>506</v>
       </c>
       <c r="B619" s="1">
         <v>1</v>
@@ -10948,7 +10948,7 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A620" s="1" t="s">
-        <v>619</v>
+        <v>507</v>
       </c>
       <c r="B620" s="1">
         <v>1</v>
@@ -10962,7 +10962,7 @@
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A621" s="1" t="s">
-        <v>620</v>
+        <v>508</v>
       </c>
       <c r="B621" s="1">
         <v>1</v>
@@ -10976,7 +10976,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A622" s="1" t="s">
-        <v>621</v>
+        <v>586</v>
       </c>
       <c r="B622" s="1">
         <v>1</v>
@@ -10990,7 +10990,7 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A623" s="1" t="s">
-        <v>622</v>
+        <v>509</v>
       </c>
       <c r="B623" s="1">
         <v>1</v>
@@ -11004,7 +11004,7 @@
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A624" s="1" t="s">
-        <v>623</v>
+        <v>510</v>
       </c>
       <c r="B624" s="1">
         <v>1</v>
@@ -11018,7 +11018,7 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A625" s="1" t="s">
-        <v>624</v>
+        <v>511</v>
       </c>
       <c r="B625" s="1">
         <v>1</v>
@@ -11030,21 +11030,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A626" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="B626" s="4">
-        <v>1</v>
-      </c>
-      <c r="C626" s="4">
-        <v>1</v>
-      </c>
-      <c r="D626" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="627" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.15"/>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A626" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B626" s="1">
+        <v>1</v>
+      </c>
+      <c r="C626" s="1">
+        <v>1</v>
+      </c>
+      <c r="D626" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A627" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B627" s="1">
+        <v>1</v>
+      </c>
+      <c r="C627" s="1">
+        <v>1</v>
+      </c>
+      <c r="D627" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A628" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B628" s="4">
+        <v>1</v>
+      </c>
+      <c r="C628" s="4">
+        <v>1</v>
+      </c>
+      <c r="D628" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
